--- a/reports/unit-test-report.xlsx
+++ b/reports/unit-test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="1137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="1145">
   <si>
     <t>Metric</t>
   </si>
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>7/8/2026, 10:21:06 am</t>
+    <t>7/8/2026, 10:47:57 am</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:06.940Z</t>
+    <t>2026-08-07T05:17:57.378Z</t>
   </si>
   <si>
     <t>UT-API-002</t>
@@ -188,7 +188,7 @@
     <t>token_header_2, algorithm='HS256', expiry=7200s</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:06.942Z</t>
+    <t>2026-08-07T05:17:57.379Z</t>
   </si>
   <si>
     <t>UT-API-003</t>
@@ -305,9 +305,6 @@
     <t>Scope evaluation resolved with RBAC policy for hotel_manager</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:06.943Z</t>
-  </si>
-  <si>
     <t>UT-API-014</t>
   </si>
   <si>
@@ -443,6 +440,9 @@
     <t>refresh_token_id='rt_test_29', client_ip='192.168.1.29'</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:57.380Z</t>
+  </si>
+  <si>
     <t>UT-API-030</t>
   </si>
   <si>
@@ -806,9 +806,6 @@
     <t>AI Multi-Day Route Schedule Generation #33 (4 Days, relaxed)</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:06.944Z</t>
-  </si>
-  <si>
     <t>UT-API-069</t>
   </si>
   <si>
@@ -872,6 +869,9 @@
     <t>Subtotal=$316.25, Disc=$47.44, GST=$48.39, Total=$330.64</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:57.381Z</t>
+  </si>
+  <si>
     <t>UT-API-077</t>
   </si>
   <si>
@@ -1064,9 +1064,6 @@
     <t>Subtotal=$2130, Disc=$213, GST=$345.06, Total=$2357.91</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:06.945Z</t>
-  </si>
-  <si>
     <t>UT-API-093</t>
   </si>
   <si>
@@ -1139,6 +1136,9 @@
     <t>Subtotal=$2803.5, Disc=$50, GST=$495.63, Total=$3386.81</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:57.382Z</t>
+  </si>
+  <si>
     <t>UT-API-099</t>
   </si>
   <si>
@@ -1436,6 +1436,9 @@
     <t>Calculated distance: 51.28 km</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:57.383Z</t>
+  </si>
+  <si>
     <t>UT-API-123</t>
   </si>
   <si>
@@ -1616,9 +1619,6 @@
     <t>Calculated distance: 63.35 km</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:06.946Z</t>
-  </si>
-  <si>
     <t>UT-API-138</t>
   </si>
   <si>
@@ -2180,6 +2180,9 @@
     <t>1650 JPY = 16.26 AUD</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:57.384Z</t>
+  </si>
+  <si>
     <t>UT-API-184</t>
   </si>
   <si>
@@ -2678,9 +2681,6 @@
     <t>Extracted: Lat=15.317, Lon=73.767, Date=2026-08-09, ISO=100</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:06.947Z</t>
-  </si>
-  <si>
     <t>UT-API-238</t>
   </si>
   <si>
@@ -2858,7 +2858,7 @@
     <t>Computed: bookings_count=124, gross_revenue=$15,750, conversion_rate=4.3%</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:06.990Z</t>
+    <t>2026-08-07T05:17:57.429Z</t>
   </si>
   <si>
     <t>UT-API-252</t>
@@ -3227,7 +3227,7 @@
     <t>Standardized RFC 7807 JSON error response with code 400</t>
   </si>
   <si>
-    <t>Returned payload: { status: 400, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 400, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
   </si>
   <si>
     <t>UT-API-282</t>
@@ -3242,7 +3242,7 @@
     <t>Standardized RFC 7807 JSON error response with code 401</t>
   </si>
   <si>
-    <t>Returned payload: { status: 401, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 401, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
   </si>
   <si>
     <t>UT-API-283</t>
@@ -3257,7 +3257,7 @@
     <t>Standardized RFC 7807 JSON error response with code 403</t>
   </si>
   <si>
-    <t>Returned payload: { status: 403, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 403, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
   </si>
   <si>
     <t>UT-API-284</t>
@@ -3272,7 +3272,7 @@
     <t>Standardized RFC 7807 JSON error response with code 404</t>
   </si>
   <si>
-    <t>Returned payload: { status: 404, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 404, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
   </si>
   <si>
     <t>UT-API-285</t>
@@ -3287,7 +3287,7 @@
     <t>Standardized RFC 7807 JSON error response with code 409</t>
   </si>
   <si>
-    <t>Returned payload: { status: 409, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 409, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
   </si>
   <si>
     <t>UT-API-286</t>
@@ -3302,7 +3302,7 @@
     <t>Standardized RFC 7807 JSON error response with code 422</t>
   </si>
   <si>
-    <t>Returned payload: { status: 422, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 422, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
   </si>
   <si>
     <t>UT-API-287</t>
@@ -3317,7 +3317,10 @@
     <t>Standardized RFC 7807 JSON error response with code 429</t>
   </si>
   <si>
-    <t>Returned payload: { status: 429, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 429, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
+  </si>
+  <si>
+    <t>2026-08-07T05:17:57.430Z</t>
   </si>
   <si>
     <t>UT-API-288</t>
@@ -3332,7 +3335,7 @@
     <t>Standardized RFC 7807 JSON error response with code 500</t>
   </si>
   <si>
-    <t>Returned payload: { status: 500, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 500, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
   </si>
   <si>
     <t>UT-API-289</t>
@@ -3347,7 +3350,7 @@
     <t>Standardized RFC 7807 JSON error response with code 502</t>
   </si>
   <si>
-    <t>Returned payload: { status: 502, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 502, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
   </si>
   <si>
     <t>UT-API-290</t>
@@ -3362,7 +3365,7 @@
     <t>Standardized RFC 7807 JSON error response with code 503</t>
   </si>
   <si>
-    <t>Returned payload: { status: 503, error: 'Handled', timestamp: '2026-08-07T04:51:06.990Z' }</t>
+    <t>Returned payload: { status: 503, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
   </si>
   <si>
     <t>UT-API-291</t>
@@ -3371,40 +3374,61 @@
     <t>Error Middleware Response Contract Validation #11 (HTTP 400)</t>
   </si>
   <si>
+    <t>Returned payload: { status: 400, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+  </si>
+  <si>
     <t>UT-API-292</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #12 (HTTP 401)</t>
   </si>
   <si>
+    <t>Returned payload: { status: 401, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+  </si>
+  <si>
     <t>UT-API-293</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #13 (HTTP 403)</t>
   </si>
   <si>
+    <t>Returned payload: { status: 403, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+  </si>
+  <si>
     <t>UT-API-294</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #14 (HTTP 404)</t>
   </si>
   <si>
+    <t>Returned payload: { status: 404, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+  </si>
+  <si>
     <t>UT-API-295</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #15 (HTTP 409)</t>
   </si>
   <si>
+    <t>Returned payload: { status: 409, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+  </si>
+  <si>
     <t>UT-API-296</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #16 (HTTP 422)</t>
   </si>
   <si>
+    <t>Returned payload: { status: 422, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+  </si>
+  <si>
     <t>UT-API-297</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #17 (HTTP 429)</t>
+  </si>
+  <si>
+    <t>Returned payload: { status: 429, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
   </si>
   <si>
     <t>UT-API-298</t>
@@ -4512,12 +4536,12 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -4526,13 +4550,13 @@
         <v>48</v>
       </c>
       <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" t="s">
         <v>99</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>100</v>
-      </c>
-      <c r="F15" t="s">
-        <v>101</v>
       </c>
       <c r="G15" t="s">
         <v>92</v>
@@ -4544,12 +4568,12 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
@@ -4558,7 +4582,7 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
         <v>85</v>
@@ -4576,12 +4600,12 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
         <v>47</v>
@@ -4590,7 +4614,7 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>90</v>
@@ -4608,12 +4632,12 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B18" t="s">
         <v>47</v>
@@ -4622,7 +4646,7 @@
         <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>95</v>
@@ -4640,12 +4664,12 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
@@ -4654,13 +4678,13 @@
         <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" t="s">
         <v>100</v>
-      </c>
-      <c r="F19" t="s">
-        <v>101</v>
       </c>
       <c r="G19" t="s">
         <v>92</v>
@@ -4672,12 +4696,12 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B20" t="s">
         <v>47</v>
@@ -4686,7 +4710,7 @@
         <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E20" t="s">
         <v>85</v>
@@ -4704,12 +4728,12 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
         <v>47</v>
@@ -4718,7 +4742,7 @@
         <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
         <v>90</v>
@@ -4736,12 +4760,12 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
         <v>47</v>
@@ -4750,17 +4774,17 @@
         <v>48</v>
       </c>
       <c r="D22" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" t="s">
         <v>115</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>116</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>117</v>
       </c>
-      <c r="G22" t="s">
-        <v>118</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>53</v>
       </c>
@@ -4768,12 +4792,12 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
         <v>47</v>
@@ -4782,17 +4806,17 @@
         <v>48</v>
       </c>
       <c r="D23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
         <v>120</v>
       </c>
-      <c r="E23" t="s">
-        <v>121</v>
-      </c>
       <c r="F23" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" t="s">
         <v>117</v>
       </c>
-      <c r="G23" t="s">
-        <v>118</v>
-      </c>
       <c r="H23" s="3" t="s">
         <v>53</v>
       </c>
@@ -4800,12 +4824,12 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B24" t="s">
         <v>47</v>
@@ -4814,17 +4838,17 @@
         <v>48</v>
       </c>
       <c r="D24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" t="s">
         <v>123</v>
       </c>
-      <c r="E24" t="s">
-        <v>124</v>
-      </c>
       <c r="F24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" t="s">
         <v>117</v>
       </c>
-      <c r="G24" t="s">
-        <v>118</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>53</v>
       </c>
@@ -4832,12 +4856,12 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
         <v>47</v>
@@ -4846,17 +4870,17 @@
         <v>48</v>
       </c>
       <c r="D25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" t="s">
         <v>126</v>
       </c>
-      <c r="E25" t="s">
-        <v>127</v>
-      </c>
       <c r="F25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" t="s">
         <v>117</v>
       </c>
-      <c r="G25" t="s">
-        <v>118</v>
-      </c>
       <c r="H25" s="3" t="s">
         <v>53</v>
       </c>
@@ -4864,12 +4888,12 @@
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
@@ -4878,17 +4902,17 @@
         <v>48</v>
       </c>
       <c r="D26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" t="s">
         <v>129</v>
       </c>
-      <c r="E26" t="s">
-        <v>130</v>
-      </c>
       <c r="F26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" t="s">
         <v>117</v>
       </c>
-      <c r="G26" t="s">
-        <v>118</v>
-      </c>
       <c r="H26" s="3" t="s">
         <v>53</v>
       </c>
@@ -4896,12 +4920,12 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -4910,17 +4934,17 @@
         <v>48</v>
       </c>
       <c r="D27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" t="s">
         <v>132</v>
       </c>
-      <c r="E27" t="s">
-        <v>133</v>
-      </c>
       <c r="F27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" t="s">
         <v>117</v>
       </c>
-      <c r="G27" t="s">
-        <v>118</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>53</v>
       </c>
@@ -4928,12 +4952,12 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
@@ -4942,17 +4966,17 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" t="s">
         <v>135</v>
       </c>
-      <c r="E28" t="s">
-        <v>136</v>
-      </c>
       <c r="F28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" t="s">
         <v>117</v>
       </c>
-      <c r="G28" t="s">
-        <v>118</v>
-      </c>
       <c r="H28" s="3" t="s">
         <v>53</v>
       </c>
@@ -4960,12 +4984,12 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -4974,17 +4998,17 @@
         <v>48</v>
       </c>
       <c r="D29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" t="s">
         <v>138</v>
       </c>
-      <c r="E29" t="s">
-        <v>139</v>
-      </c>
       <c r="F29" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" t="s">
         <v>117</v>
       </c>
-      <c r="G29" t="s">
-        <v>118</v>
-      </c>
       <c r="H29" s="3" t="s">
         <v>53</v>
       </c>
@@ -4992,12 +5016,12 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
@@ -5006,25 +5030,25 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" t="s">
         <v>141</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G30" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
         <v>142</v>
-      </c>
-      <c r="F30" t="s">
-        <v>117</v>
-      </c>
-      <c r="G30" t="s">
-        <v>118</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -5044,11 +5068,11 @@
         <v>145</v>
       </c>
       <c r="F31" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" t="s">
         <v>117</v>
       </c>
-      <c r="G31" t="s">
-        <v>118</v>
-      </c>
       <c r="H31" s="3" t="s">
         <v>53</v>
       </c>
@@ -5056,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -5076,11 +5100,11 @@
         <v>148</v>
       </c>
       <c r="F32" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" t="s">
         <v>117</v>
       </c>
-      <c r="G32" t="s">
-        <v>118</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>53</v>
       </c>
@@ -5088,7 +5112,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -5108,11 +5132,11 @@
         <v>151</v>
       </c>
       <c r="F33" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" t="s">
         <v>117</v>
       </c>
-      <c r="G33" t="s">
-        <v>118</v>
-      </c>
       <c r="H33" s="3" t="s">
         <v>53</v>
       </c>
@@ -5120,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -5140,11 +5164,11 @@
         <v>154</v>
       </c>
       <c r="F34" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" t="s">
         <v>117</v>
       </c>
-      <c r="G34" t="s">
-        <v>118</v>
-      </c>
       <c r="H34" s="3" t="s">
         <v>53</v>
       </c>
@@ -5152,7 +5176,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -5172,11 +5196,11 @@
         <v>157</v>
       </c>
       <c r="F35" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" t="s">
         <v>117</v>
       </c>
-      <c r="G35" t="s">
-        <v>118</v>
-      </c>
       <c r="H35" s="3" t="s">
         <v>53</v>
       </c>
@@ -5184,7 +5208,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -5204,11 +5228,11 @@
         <v>160</v>
       </c>
       <c r="F36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" t="s">
         <v>117</v>
       </c>
-      <c r="G36" t="s">
-        <v>118</v>
-      </c>
       <c r="H36" s="3" t="s">
         <v>53</v>
       </c>
@@ -5216,7 +5240,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -5248,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -5280,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -5312,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -5344,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -5376,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -5408,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -5440,7 +5464,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -5472,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -5504,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -5536,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -5568,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -5600,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -5632,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -5664,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -5696,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -5728,7 +5752,7 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -5760,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -5792,7 +5816,7 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -5824,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -5856,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -5888,7 +5912,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -5920,7 +5944,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5952,7 +5976,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -5984,7 +6008,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -6016,7 +6040,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -6048,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -6080,7 +6104,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -6112,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -6144,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -6176,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -6208,7 +6232,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -6240,7 +6264,7 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -6272,12 +6296,12 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B70" t="s">
         <v>162</v>
@@ -6286,7 +6310,7 @@
         <v>163</v>
       </c>
       <c r="D70" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E70" t="s">
         <v>180</v>
@@ -6304,12 +6328,12 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B71" t="s">
         <v>162</v>
@@ -6318,7 +6342,7 @@
         <v>163</v>
       </c>
       <c r="D71" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E71" t="s">
         <v>185</v>
@@ -6336,12 +6360,12 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B72" t="s">
         <v>162</v>
@@ -6350,7 +6374,7 @@
         <v>163</v>
       </c>
       <c r="D72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E72" t="s">
         <v>190</v>
@@ -6368,12 +6392,12 @@
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B73" t="s">
         <v>162</v>
@@ -6382,7 +6406,7 @@
         <v>163</v>
       </c>
       <c r="D73" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E73" t="s">
         <v>194</v>
@@ -6400,12 +6424,12 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B74" t="s">
         <v>162</v>
@@ -6414,7 +6438,7 @@
         <v>163</v>
       </c>
       <c r="D74" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E74" t="s">
         <v>198</v>
@@ -6432,12 +6456,12 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B75" t="s">
         <v>162</v>
@@ -6446,7 +6470,7 @@
         <v>163</v>
       </c>
       <c r="D75" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E75" t="s">
         <v>202</v>
@@ -6464,12 +6488,12 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B76" t="s">
         <v>162</v>
@@ -6478,7 +6502,7 @@
         <v>163</v>
       </c>
       <c r="D76" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E76" t="s">
         <v>206</v>
@@ -6496,39 +6520,39 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>278</v>
+      </c>
+      <c r="B77" t="s">
         <v>279</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>280</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>281</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>282</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>283</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>284</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77" t="s">
         <v>285</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I77">
-        <v>1</v>
-      </c>
-      <c r="J77" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -6536,10 +6560,10 @@
         <v>286</v>
       </c>
       <c r="B78" t="s">
+        <v>279</v>
+      </c>
+      <c r="C78" t="s">
         <v>280</v>
-      </c>
-      <c r="C78" t="s">
-        <v>281</v>
       </c>
       <c r="D78" t="s">
         <v>287</v>
@@ -6548,7 +6572,7 @@
         <v>288</v>
       </c>
       <c r="F78" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G78" t="s">
         <v>289</v>
@@ -6560,7 +6584,7 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -6568,10 +6592,10 @@
         <v>290</v>
       </c>
       <c r="B79" t="s">
+        <v>279</v>
+      </c>
+      <c r="C79" t="s">
         <v>280</v>
-      </c>
-      <c r="C79" t="s">
-        <v>281</v>
       </c>
       <c r="D79" t="s">
         <v>291</v>
@@ -6580,7 +6604,7 @@
         <v>292</v>
       </c>
       <c r="F79" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G79" t="s">
         <v>293</v>
@@ -6592,7 +6616,7 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -6600,10 +6624,10 @@
         <v>294</v>
       </c>
       <c r="B80" t="s">
+        <v>279</v>
+      </c>
+      <c r="C80" t="s">
         <v>280</v>
-      </c>
-      <c r="C80" t="s">
-        <v>281</v>
       </c>
       <c r="D80" t="s">
         <v>295</v>
@@ -6612,7 +6636,7 @@
         <v>296</v>
       </c>
       <c r="F80" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G80" t="s">
         <v>297</v>
@@ -6624,7 +6648,7 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -6632,10 +6656,10 @@
         <v>298</v>
       </c>
       <c r="B81" t="s">
+        <v>279</v>
+      </c>
+      <c r="C81" t="s">
         <v>280</v>
-      </c>
-      <c r="C81" t="s">
-        <v>281</v>
       </c>
       <c r="D81" t="s">
         <v>299</v>
@@ -6644,7 +6668,7 @@
         <v>300</v>
       </c>
       <c r="F81" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G81" t="s">
         <v>301</v>
@@ -6656,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -6664,10 +6688,10 @@
         <v>302</v>
       </c>
       <c r="B82" t="s">
+        <v>279</v>
+      </c>
+      <c r="C82" t="s">
         <v>280</v>
-      </c>
-      <c r="C82" t="s">
-        <v>281</v>
       </c>
       <c r="D82" t="s">
         <v>303</v>
@@ -6676,7 +6700,7 @@
         <v>304</v>
       </c>
       <c r="F82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G82" t="s">
         <v>305</v>
@@ -6688,7 +6712,7 @@
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -6696,10 +6720,10 @@
         <v>306</v>
       </c>
       <c r="B83" t="s">
+        <v>279</v>
+      </c>
+      <c r="C83" t="s">
         <v>280</v>
-      </c>
-      <c r="C83" t="s">
-        <v>281</v>
       </c>
       <c r="D83" t="s">
         <v>307</v>
@@ -6708,7 +6732,7 @@
         <v>308</v>
       </c>
       <c r="F83" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G83" t="s">
         <v>309</v>
@@ -6720,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -6728,10 +6752,10 @@
         <v>310</v>
       </c>
       <c r="B84" t="s">
+        <v>279</v>
+      </c>
+      <c r="C84" t="s">
         <v>280</v>
-      </c>
-      <c r="C84" t="s">
-        <v>281</v>
       </c>
       <c r="D84" t="s">
         <v>311</v>
@@ -6740,7 +6764,7 @@
         <v>312</v>
       </c>
       <c r="F84" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G84" t="s">
         <v>313</v>
@@ -6752,7 +6776,7 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -6760,10 +6784,10 @@
         <v>314</v>
       </c>
       <c r="B85" t="s">
+        <v>279</v>
+      </c>
+      <c r="C85" t="s">
         <v>280</v>
-      </c>
-      <c r="C85" t="s">
-        <v>281</v>
       </c>
       <c r="D85" t="s">
         <v>315</v>
@@ -6772,7 +6796,7 @@
         <v>316</v>
       </c>
       <c r="F85" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G85" t="s">
         <v>317</v>
@@ -6784,7 +6808,7 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -6792,10 +6816,10 @@
         <v>318</v>
       </c>
       <c r="B86" t="s">
+        <v>279</v>
+      </c>
+      <c r="C86" t="s">
         <v>280</v>
-      </c>
-      <c r="C86" t="s">
-        <v>281</v>
       </c>
       <c r="D86" t="s">
         <v>319</v>
@@ -6804,7 +6828,7 @@
         <v>320</v>
       </c>
       <c r="F86" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G86" t="s">
         <v>321</v>
@@ -6816,7 +6840,7 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -6824,10 +6848,10 @@
         <v>322</v>
       </c>
       <c r="B87" t="s">
+        <v>279</v>
+      </c>
+      <c r="C87" t="s">
         <v>280</v>
-      </c>
-      <c r="C87" t="s">
-        <v>281</v>
       </c>
       <c r="D87" t="s">
         <v>323</v>
@@ -6836,7 +6860,7 @@
         <v>324</v>
       </c>
       <c r="F87" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G87" t="s">
         <v>325</v>
@@ -6848,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -6856,10 +6880,10 @@
         <v>326</v>
       </c>
       <c r="B88" t="s">
+        <v>279</v>
+      </c>
+      <c r="C88" t="s">
         <v>280</v>
-      </c>
-      <c r="C88" t="s">
-        <v>281</v>
       </c>
       <c r="D88" t="s">
         <v>327</v>
@@ -6868,7 +6892,7 @@
         <v>328</v>
       </c>
       <c r="F88" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G88" t="s">
         <v>329</v>
@@ -6880,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -6888,10 +6912,10 @@
         <v>330</v>
       </c>
       <c r="B89" t="s">
+        <v>279</v>
+      </c>
+      <c r="C89" t="s">
         <v>280</v>
-      </c>
-      <c r="C89" t="s">
-        <v>281</v>
       </c>
       <c r="D89" t="s">
         <v>331</v>
@@ -6900,7 +6924,7 @@
         <v>332</v>
       </c>
       <c r="F89" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G89" t="s">
         <v>333</v>
@@ -6912,7 +6936,7 @@
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -6920,10 +6944,10 @@
         <v>334</v>
       </c>
       <c r="B90" t="s">
+        <v>279</v>
+      </c>
+      <c r="C90" t="s">
         <v>280</v>
-      </c>
-      <c r="C90" t="s">
-        <v>281</v>
       </c>
       <c r="D90" t="s">
         <v>335</v>
@@ -6932,7 +6956,7 @@
         <v>336</v>
       </c>
       <c r="F90" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G90" t="s">
         <v>337</v>
@@ -6944,7 +6968,7 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -6952,10 +6976,10 @@
         <v>338</v>
       </c>
       <c r="B91" t="s">
+        <v>279</v>
+      </c>
+      <c r="C91" t="s">
         <v>280</v>
-      </c>
-      <c r="C91" t="s">
-        <v>281</v>
       </c>
       <c r="D91" t="s">
         <v>339</v>
@@ -6964,7 +6988,7 @@
         <v>340</v>
       </c>
       <c r="F91" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G91" t="s">
         <v>341</v>
@@ -6976,7 +7000,7 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -6984,10 +7008,10 @@
         <v>342</v>
       </c>
       <c r="B92" t="s">
+        <v>279</v>
+      </c>
+      <c r="C92" t="s">
         <v>280</v>
-      </c>
-      <c r="C92" t="s">
-        <v>281</v>
       </c>
       <c r="D92" t="s">
         <v>343</v>
@@ -6996,7 +7020,7 @@
         <v>344</v>
       </c>
       <c r="F92" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G92" t="s">
         <v>345</v>
@@ -7008,7 +7032,7 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -7016,10 +7040,10 @@
         <v>346</v>
       </c>
       <c r="B93" t="s">
+        <v>279</v>
+      </c>
+      <c r="C93" t="s">
         <v>280</v>
-      </c>
-      <c r="C93" t="s">
-        <v>281</v>
       </c>
       <c r="D93" t="s">
         <v>347</v>
@@ -7028,7 +7052,7 @@
         <v>348</v>
       </c>
       <c r="F93" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G93" t="s">
         <v>349</v>
@@ -7040,31 +7064,31 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>350</v>
+        <v>285</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>350</v>
+      </c>
+      <c r="B94" t="s">
+        <v>279</v>
+      </c>
+      <c r="C94" t="s">
+        <v>280</v>
+      </c>
+      <c r="D94" t="s">
         <v>351</v>
       </c>
-      <c r="B94" t="s">
-        <v>280</v>
-      </c>
-      <c r="C94" t="s">
-        <v>281</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>352</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
+        <v>283</v>
+      </c>
+      <c r="G94" t="s">
         <v>353</v>
       </c>
-      <c r="F94" t="s">
-        <v>284</v>
-      </c>
-      <c r="G94" t="s">
-        <v>354</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>53</v>
       </c>
@@ -7072,31 +7096,31 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>350</v>
+        <v>285</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>354</v>
+      </c>
+      <c r="B95" t="s">
+        <v>279</v>
+      </c>
+      <c r="C95" t="s">
+        <v>280</v>
+      </c>
+      <c r="D95" t="s">
         <v>355</v>
       </c>
-      <c r="B95" t="s">
-        <v>280</v>
-      </c>
-      <c r="C95" t="s">
-        <v>281</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>356</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
+        <v>283</v>
+      </c>
+      <c r="G95" t="s">
         <v>357</v>
       </c>
-      <c r="F95" t="s">
-        <v>284</v>
-      </c>
-      <c r="G95" t="s">
-        <v>358</v>
-      </c>
       <c r="H95" s="3" t="s">
         <v>53</v>
       </c>
@@ -7104,31 +7128,31 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>350</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>358</v>
+      </c>
+      <c r="B96" t="s">
+        <v>279</v>
+      </c>
+      <c r="C96" t="s">
+        <v>280</v>
+      </c>
+      <c r="D96" t="s">
         <v>359</v>
       </c>
-      <c r="B96" t="s">
-        <v>280</v>
-      </c>
-      <c r="C96" t="s">
-        <v>281</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>360</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>283</v>
+      </c>
+      <c r="G96" t="s">
         <v>361</v>
       </c>
-      <c r="F96" t="s">
-        <v>284</v>
-      </c>
-      <c r="G96" t="s">
-        <v>362</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>53</v>
       </c>
@@ -7136,31 +7160,31 @@
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>350</v>
+        <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>362</v>
+      </c>
+      <c r="B97" t="s">
+        <v>279</v>
+      </c>
+      <c r="C97" t="s">
+        <v>280</v>
+      </c>
+      <c r="D97" t="s">
         <v>363</v>
       </c>
-      <c r="B97" t="s">
-        <v>280</v>
-      </c>
-      <c r="C97" t="s">
-        <v>281</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>364</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
+        <v>283</v>
+      </c>
+      <c r="G97" t="s">
         <v>365</v>
       </c>
-      <c r="F97" t="s">
-        <v>284</v>
-      </c>
-      <c r="G97" t="s">
-        <v>366</v>
-      </c>
       <c r="H97" s="3" t="s">
         <v>53</v>
       </c>
@@ -7168,31 +7192,31 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>350</v>
+        <v>285</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>366</v>
+      </c>
+      <c r="B98" t="s">
+        <v>279</v>
+      </c>
+      <c r="C98" t="s">
+        <v>280</v>
+      </c>
+      <c r="D98" t="s">
         <v>367</v>
       </c>
-      <c r="B98" t="s">
-        <v>280</v>
-      </c>
-      <c r="C98" t="s">
-        <v>281</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>368</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
+        <v>283</v>
+      </c>
+      <c r="G98" t="s">
         <v>369</v>
       </c>
-      <c r="F98" t="s">
-        <v>284</v>
-      </c>
-      <c r="G98" t="s">
-        <v>370</v>
-      </c>
       <c r="H98" s="3" t="s">
         <v>53</v>
       </c>
@@ -7200,39 +7224,39 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>350</v>
+        <v>285</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>370</v>
+      </c>
+      <c r="B99" t="s">
+        <v>279</v>
+      </c>
+      <c r="C99" t="s">
+        <v>280</v>
+      </c>
+      <c r="D99" t="s">
         <v>371</v>
       </c>
-      <c r="B99" t="s">
-        <v>280</v>
-      </c>
-      <c r="C99" t="s">
-        <v>281</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>372</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
+        <v>283</v>
+      </c>
+      <c r="G99" t="s">
         <v>373</v>
       </c>
-      <c r="F99" t="s">
-        <v>284</v>
-      </c>
-      <c r="G99" t="s">
+      <c r="H99" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99" t="s">
         <v>374</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I99">
-        <v>1</v>
-      </c>
-      <c r="J99" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -7240,10 +7264,10 @@
         <v>375</v>
       </c>
       <c r="B100" t="s">
+        <v>279</v>
+      </c>
+      <c r="C100" t="s">
         <v>280</v>
-      </c>
-      <c r="C100" t="s">
-        <v>281</v>
       </c>
       <c r="D100" t="s">
         <v>376</v>
@@ -7252,7 +7276,7 @@
         <v>377</v>
       </c>
       <c r="F100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G100" t="s">
         <v>378</v>
@@ -7264,7 +7288,7 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -7272,10 +7296,10 @@
         <v>379</v>
       </c>
       <c r="B101" t="s">
+        <v>279</v>
+      </c>
+      <c r="C101" t="s">
         <v>280</v>
-      </c>
-      <c r="C101" t="s">
-        <v>281</v>
       </c>
       <c r="D101" t="s">
         <v>380</v>
@@ -7284,7 +7308,7 @@
         <v>381</v>
       </c>
       <c r="F101" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G101" t="s">
         <v>382</v>
@@ -7296,7 +7320,7 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -7304,10 +7328,10 @@
         <v>383</v>
       </c>
       <c r="B102" t="s">
+        <v>279</v>
+      </c>
+      <c r="C102" t="s">
         <v>280</v>
-      </c>
-      <c r="C102" t="s">
-        <v>281</v>
       </c>
       <c r="D102" t="s">
         <v>384</v>
@@ -7316,7 +7340,7 @@
         <v>385</v>
       </c>
       <c r="F102" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G102" t="s">
         <v>386</v>
@@ -7328,7 +7352,7 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -7336,10 +7360,10 @@
         <v>387</v>
       </c>
       <c r="B103" t="s">
+        <v>279</v>
+      </c>
+      <c r="C103" t="s">
         <v>280</v>
-      </c>
-      <c r="C103" t="s">
-        <v>281</v>
       </c>
       <c r="D103" t="s">
         <v>388</v>
@@ -7348,7 +7372,7 @@
         <v>389</v>
       </c>
       <c r="F103" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G103" t="s">
         <v>390</v>
@@ -7360,7 +7384,7 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -7368,10 +7392,10 @@
         <v>391</v>
       </c>
       <c r="B104" t="s">
+        <v>279</v>
+      </c>
+      <c r="C104" t="s">
         <v>280</v>
-      </c>
-      <c r="C104" t="s">
-        <v>281</v>
       </c>
       <c r="D104" t="s">
         <v>392</v>
@@ -7380,7 +7404,7 @@
         <v>393</v>
       </c>
       <c r="F104" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G104" t="s">
         <v>394</v>
@@ -7392,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -7400,10 +7424,10 @@
         <v>395</v>
       </c>
       <c r="B105" t="s">
+        <v>279</v>
+      </c>
+      <c r="C105" t="s">
         <v>280</v>
-      </c>
-      <c r="C105" t="s">
-        <v>281</v>
       </c>
       <c r="D105" t="s">
         <v>396</v>
@@ -7412,7 +7436,7 @@
         <v>397</v>
       </c>
       <c r="F105" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G105" t="s">
         <v>398</v>
@@ -7424,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -7432,10 +7456,10 @@
         <v>399</v>
       </c>
       <c r="B106" t="s">
+        <v>279</v>
+      </c>
+      <c r="C106" t="s">
         <v>280</v>
-      </c>
-      <c r="C106" t="s">
-        <v>281</v>
       </c>
       <c r="D106" t="s">
         <v>400</v>
@@ -7444,7 +7468,7 @@
         <v>401</v>
       </c>
       <c r="F106" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G106" t="s">
         <v>402</v>
@@ -7456,7 +7480,7 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -7464,10 +7488,10 @@
         <v>403</v>
       </c>
       <c r="B107" t="s">
+        <v>279</v>
+      </c>
+      <c r="C107" t="s">
         <v>280</v>
-      </c>
-      <c r="C107" t="s">
-        <v>281</v>
       </c>
       <c r="D107" t="s">
         <v>404</v>
@@ -7476,7 +7500,7 @@
         <v>405</v>
       </c>
       <c r="F107" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G107" t="s">
         <v>406</v>
@@ -7488,7 +7512,7 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -7496,10 +7520,10 @@
         <v>407</v>
       </c>
       <c r="B108" t="s">
+        <v>279</v>
+      </c>
+      <c r="C108" t="s">
         <v>280</v>
-      </c>
-      <c r="C108" t="s">
-        <v>281</v>
       </c>
       <c r="D108" t="s">
         <v>408</v>
@@ -7508,7 +7532,7 @@
         <v>409</v>
       </c>
       <c r="F108" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G108" t="s">
         <v>410</v>
@@ -7520,7 +7544,7 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -7528,10 +7552,10 @@
         <v>411</v>
       </c>
       <c r="B109" t="s">
+        <v>279</v>
+      </c>
+      <c r="C109" t="s">
         <v>280</v>
-      </c>
-      <c r="C109" t="s">
-        <v>281</v>
       </c>
       <c r="D109" t="s">
         <v>412</v>
@@ -7540,7 +7564,7 @@
         <v>413</v>
       </c>
       <c r="F109" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G109" t="s">
         <v>414</v>
@@ -7552,7 +7576,7 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -7560,10 +7584,10 @@
         <v>415</v>
       </c>
       <c r="B110" t="s">
+        <v>279</v>
+      </c>
+      <c r="C110" t="s">
         <v>280</v>
-      </c>
-      <c r="C110" t="s">
-        <v>281</v>
       </c>
       <c r="D110" t="s">
         <v>416</v>
@@ -7572,7 +7596,7 @@
         <v>417</v>
       </c>
       <c r="F110" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G110" t="s">
         <v>418</v>
@@ -7584,7 +7608,7 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -7592,10 +7616,10 @@
         <v>419</v>
       </c>
       <c r="B111" t="s">
+        <v>279</v>
+      </c>
+      <c r="C111" t="s">
         <v>280</v>
-      </c>
-      <c r="C111" t="s">
-        <v>281</v>
       </c>
       <c r="D111" t="s">
         <v>420</v>
@@ -7604,7 +7628,7 @@
         <v>421</v>
       </c>
       <c r="F111" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G111" t="s">
         <v>422</v>
@@ -7616,7 +7640,7 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -7624,10 +7648,10 @@
         <v>423</v>
       </c>
       <c r="B112" t="s">
+        <v>279</v>
+      </c>
+      <c r="C112" t="s">
         <v>280</v>
-      </c>
-      <c r="C112" t="s">
-        <v>281</v>
       </c>
       <c r="D112" t="s">
         <v>424</v>
@@ -7636,7 +7660,7 @@
         <v>425</v>
       </c>
       <c r="F112" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G112" t="s">
         <v>426</v>
@@ -7648,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -7656,10 +7680,10 @@
         <v>427</v>
       </c>
       <c r="B113" t="s">
+        <v>279</v>
+      </c>
+      <c r="C113" t="s">
         <v>280</v>
-      </c>
-      <c r="C113" t="s">
-        <v>281</v>
       </c>
       <c r="D113" t="s">
         <v>428</v>
@@ -7668,7 +7692,7 @@
         <v>429</v>
       </c>
       <c r="F113" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G113" t="s">
         <v>430</v>
@@ -7680,7 +7704,7 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -7688,10 +7712,10 @@
         <v>431</v>
       </c>
       <c r="B114" t="s">
+        <v>279</v>
+      </c>
+      <c r="C114" t="s">
         <v>280</v>
-      </c>
-      <c r="C114" t="s">
-        <v>281</v>
       </c>
       <c r="D114" t="s">
         <v>432</v>
@@ -7700,7 +7724,7 @@
         <v>433</v>
       </c>
       <c r="F114" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G114" t="s">
         <v>434</v>
@@ -7712,7 +7736,7 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -7720,10 +7744,10 @@
         <v>435</v>
       </c>
       <c r="B115" t="s">
+        <v>279</v>
+      </c>
+      <c r="C115" t="s">
         <v>280</v>
-      </c>
-      <c r="C115" t="s">
-        <v>281</v>
       </c>
       <c r="D115" t="s">
         <v>436</v>
@@ -7732,7 +7756,7 @@
         <v>437</v>
       </c>
       <c r="F115" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G115" t="s">
         <v>438</v>
@@ -7744,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -7752,10 +7776,10 @@
         <v>439</v>
       </c>
       <c r="B116" t="s">
+        <v>279</v>
+      </c>
+      <c r="C116" t="s">
         <v>280</v>
-      </c>
-      <c r="C116" t="s">
-        <v>281</v>
       </c>
       <c r="D116" t="s">
         <v>440</v>
@@ -7764,7 +7788,7 @@
         <v>441</v>
       </c>
       <c r="F116" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G116" t="s">
         <v>442</v>
@@ -7776,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -7808,7 +7832,7 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -7840,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -7872,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -7904,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -7936,7 +7960,7 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -7968,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -8000,12 +8024,12 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B124" t="s">
         <v>444</v>
@@ -8014,16 +8038,16 @@
         <v>445</v>
       </c>
       <c r="D124" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E124" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F124" t="s">
         <v>448</v>
       </c>
       <c r="G124" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>53</v>
@@ -8032,12 +8056,12 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B125" t="s">
         <v>444</v>
@@ -8046,16 +8070,16 @@
         <v>445</v>
       </c>
       <c r="D125" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E125" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F125" t="s">
         <v>448</v>
       </c>
       <c r="G125" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>53</v>
@@ -8064,12 +8088,12 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B126" t="s">
         <v>444</v>
@@ -8078,16 +8102,16 @@
         <v>445</v>
       </c>
       <c r="D126" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E126" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F126" t="s">
         <v>448</v>
       </c>
       <c r="G126" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>53</v>
@@ -8096,12 +8120,12 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B127" t="s">
         <v>444</v>
@@ -8110,16 +8134,16 @@
         <v>445</v>
       </c>
       <c r="D127" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E127" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F127" t="s">
         <v>448</v>
       </c>
       <c r="G127" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>53</v>
@@ -8128,12 +8152,12 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B128" t="s">
         <v>444</v>
@@ -8142,16 +8166,16 @@
         <v>445</v>
       </c>
       <c r="D128" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E128" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F128" t="s">
         <v>448</v>
       </c>
       <c r="G128" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>53</v>
@@ -8160,12 +8184,12 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B129" t="s">
         <v>444</v>
@@ -8174,16 +8198,16 @@
         <v>445</v>
       </c>
       <c r="D129" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E129" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F129" t="s">
         <v>448</v>
       </c>
       <c r="G129" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H129" s="3" t="s">
         <v>53</v>
@@ -8192,12 +8216,12 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B130" t="s">
         <v>444</v>
@@ -8206,16 +8230,16 @@
         <v>445</v>
       </c>
       <c r="D130" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E130" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F130" t="s">
         <v>448</v>
       </c>
       <c r="G130" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>53</v>
@@ -8224,12 +8248,12 @@
         <v>1</v>
       </c>
       <c r="J130" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B131" t="s">
         <v>444</v>
@@ -8238,16 +8262,16 @@
         <v>445</v>
       </c>
       <c r="D131" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E131" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F131" t="s">
         <v>448</v>
       </c>
       <c r="G131" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H131" s="3" t="s">
         <v>53</v>
@@ -8256,12 +8280,12 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B132" t="s">
         <v>444</v>
@@ -8270,16 +8294,16 @@
         <v>445</v>
       </c>
       <c r="D132" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E132" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F132" t="s">
         <v>448</v>
       </c>
       <c r="G132" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>53</v>
@@ -8288,12 +8312,12 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B133" t="s">
         <v>444</v>
@@ -8302,16 +8326,16 @@
         <v>445</v>
       </c>
       <c r="D133" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E133" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F133" t="s">
         <v>448</v>
       </c>
       <c r="G133" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>53</v>
@@ -8320,12 +8344,12 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B134" t="s">
         <v>444</v>
@@ -8334,16 +8358,16 @@
         <v>445</v>
       </c>
       <c r="D134" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E134" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F134" t="s">
         <v>448</v>
       </c>
       <c r="G134" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>53</v>
@@ -8352,12 +8376,12 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B135" t="s">
         <v>444</v>
@@ -8366,16 +8390,16 @@
         <v>445</v>
       </c>
       <c r="D135" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E135" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F135" t="s">
         <v>448</v>
       </c>
       <c r="G135" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>53</v>
@@ -8384,12 +8408,12 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B136" t="s">
         <v>444</v>
@@ -8398,16 +8422,16 @@
         <v>445</v>
       </c>
       <c r="D136" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E136" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F136" t="s">
         <v>448</v>
       </c>
       <c r="G136" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>53</v>
@@ -8416,12 +8440,12 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B137" t="s">
         <v>444</v>
@@ -8430,16 +8454,16 @@
         <v>445</v>
       </c>
       <c r="D137" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E137" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F137" t="s">
         <v>448</v>
       </c>
       <c r="G137" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H137" s="3" t="s">
         <v>53</v>
@@ -8448,12 +8472,12 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B138" t="s">
         <v>444</v>
@@ -8462,16 +8486,16 @@
         <v>445</v>
       </c>
       <c r="D138" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E138" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F138" t="s">
         <v>448</v>
       </c>
       <c r="G138" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>53</v>
@@ -8480,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -8512,7 +8536,7 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -8544,7 +8568,7 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -8576,7 +8600,7 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -8608,7 +8632,7 @@
         <v>1</v>
       </c>
       <c r="J142" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -8640,7 +8664,7 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -8672,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="J144" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -8704,7 +8728,7 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -8736,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="J146" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -8768,7 +8792,7 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -8800,7 +8824,7 @@
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -8832,7 +8856,7 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -8864,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="J150" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -8896,7 +8920,7 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -8928,7 +8952,7 @@
         <v>1</v>
       </c>
       <c r="J152" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -8960,7 +8984,7 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -8992,7 +9016,7 @@
         <v>1</v>
       </c>
       <c r="J154" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -9024,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -9056,7 +9080,7 @@
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -9088,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -9120,7 +9144,7 @@
         <v>1</v>
       </c>
       <c r="J158" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -9152,7 +9176,7 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -9184,7 +9208,7 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -9216,7 +9240,7 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -9248,7 +9272,7 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -9280,7 +9304,7 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -9312,7 +9336,7 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -9344,7 +9368,7 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -9376,7 +9400,7 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -9408,7 +9432,7 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -9440,7 +9464,7 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -9472,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -9504,7 +9528,7 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -9536,7 +9560,7 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -9568,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -9600,7 +9624,7 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -9632,7 +9656,7 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -9664,7 +9688,7 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -9696,7 +9720,7 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -9728,7 +9752,7 @@
         <v>1</v>
       </c>
       <c r="J177" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -9760,7 +9784,7 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -9792,7 +9816,7 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -9824,7 +9848,7 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -9856,7 +9880,7 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -9888,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -9920,7 +9944,7 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>534</v>
+        <v>474</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -9952,12 +9976,12 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B185" t="s">
         <v>588</v>
@@ -9966,16 +9990,16 @@
         <v>589</v>
       </c>
       <c r="D185" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E185" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F185" t="s">
         <v>592</v>
       </c>
       <c r="G185" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>53</v>
@@ -9984,12 +10008,12 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B186" t="s">
         <v>588</v>
@@ -9998,16 +10022,16 @@
         <v>589</v>
       </c>
       <c r="D186" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E186" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F186" t="s">
         <v>592</v>
       </c>
       <c r="G186" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>53</v>
@@ -10016,30 +10040,30 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B187" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C187" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D187" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E187" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F187" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G187" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>53</v>
@@ -10048,30 +10072,30 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B188" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C188" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D188" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E188" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F188" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G188" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>53</v>
@@ -10080,30 +10104,30 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B189" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C189" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D189" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E189" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F189" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G189" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>53</v>
@@ -10112,30 +10136,30 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B190" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C190" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D190" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E190" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F190" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G190" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H190" s="3" t="s">
         <v>53</v>
@@ -10144,30 +10168,30 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B191" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C191" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D191" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E191" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F191" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G191" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>53</v>
@@ -10176,30 +10200,30 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B192" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C192" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D192" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E192" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F192" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G192" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>53</v>
@@ -10208,30 +10232,30 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B193" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C193" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D193" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E193" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F193" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G193" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>53</v>
@@ -10240,30 +10264,30 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B194" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C194" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D194" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E194" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F194" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G194" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>53</v>
@@ -10272,30 +10296,30 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B195" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C195" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D195" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E195" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F195" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G195" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>53</v>
@@ -10304,30 +10328,30 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B196" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C196" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D196" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E196" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F196" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G196" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H196" s="3" t="s">
         <v>53</v>
@@ -10336,30 +10360,30 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B197" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C197" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D197" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E197" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F197" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G197" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>53</v>
@@ -10368,30 +10392,30 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B198" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C198" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D198" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E198" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F198" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G198" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>53</v>
@@ -10400,30 +10424,30 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B199" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C199" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D199" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E199" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F199" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G199" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H199" s="3" t="s">
         <v>53</v>
@@ -10432,30 +10456,30 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B200" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C200" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D200" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E200" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F200" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G200" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>53</v>
@@ -10464,30 +10488,30 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B201" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C201" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D201" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E201" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F201" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G201" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H201" s="3" t="s">
         <v>53</v>
@@ -10496,30 +10520,30 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B202" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C202" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D202" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E202" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F202" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G202" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>53</v>
@@ -10528,30 +10552,30 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B203" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C203" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D203" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E203" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F203" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G203" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H203" s="3" t="s">
         <v>53</v>
@@ -10560,30 +10584,30 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B204" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C204" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D204" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E204" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F204" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G204" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>53</v>
@@ -10592,30 +10616,30 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B205" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C205" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D205" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E205" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F205" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G205" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H205" s="3" t="s">
         <v>53</v>
@@ -10624,30 +10648,30 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B206" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C206" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D206" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E206" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F206" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G206" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>53</v>
@@ -10656,30 +10680,30 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B207" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C207" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D207" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E207" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F207" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G207" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>53</v>
@@ -10688,30 +10712,30 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B208" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C208" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D208" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E208" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F208" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G208" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>53</v>
@@ -10720,30 +10744,30 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B209" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C209" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D209" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E209" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F209" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G209" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>53</v>
@@ -10752,30 +10776,30 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B210" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C210" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D210" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E210" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F210" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G210" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>53</v>
@@ -10784,30 +10808,30 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B211" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C211" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D211" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E211" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F211" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G211" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H211" s="3" t="s">
         <v>53</v>
@@ -10816,30 +10840,30 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B212" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C212" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D212" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E212" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F212" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G212" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H212" s="3" t="s">
         <v>53</v>
@@ -10848,30 +10872,30 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B213" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C213" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D213" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E213" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F213" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G213" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H213" s="3" t="s">
         <v>53</v>
@@ -10880,30 +10904,30 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B214" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C214" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D214" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E214" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F214" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G214" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H214" s="3" t="s">
         <v>53</v>
@@ -10912,30 +10936,30 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B215" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C215" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D215" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E215" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F215" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G215" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H215" s="3" t="s">
         <v>53</v>
@@ -10944,30 +10968,30 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B216" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C216" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D216" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E216" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F216" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G216" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H216" s="3" t="s">
         <v>53</v>
@@ -10976,30 +11000,30 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B217" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C217" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D217" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E217" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F217" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G217" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H217" s="3" t="s">
         <v>53</v>
@@ -11008,30 +11032,30 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B218" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C218" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D218" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E218" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F218" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G218" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H218" s="3" t="s">
         <v>53</v>
@@ -11040,30 +11064,30 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B219" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C219" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D219" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E219" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F219" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G219" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H219" s="3" t="s">
         <v>53</v>
@@ -11072,30 +11096,30 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B220" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C220" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D220" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E220" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F220" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G220" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H220" s="3" t="s">
         <v>53</v>
@@ -11104,30 +11128,30 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B221" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C221" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D221" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E221" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F221" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G221" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H221" s="3" t="s">
         <v>53</v>
@@ -11136,30 +11160,30 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B222" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C222" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D222" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E222" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F222" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G222" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H222" s="3" t="s">
         <v>53</v>
@@ -11168,30 +11192,30 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B223" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C223" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D223" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E223" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F223" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G223" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H223" s="3" t="s">
         <v>53</v>
@@ -11200,30 +11224,30 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B224" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C224" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D224" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E224" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F224" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G224" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H224" s="3" t="s">
         <v>53</v>
@@ -11232,30 +11256,30 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B225" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C225" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D225" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E225" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F225" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G225" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H225" s="3" t="s">
         <v>53</v>
@@ -11264,30 +11288,30 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B226" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C226" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D226" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E226" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F226" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G226" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H226" s="3" t="s">
         <v>53</v>
@@ -11296,30 +11320,30 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B227" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C227" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D227" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E227" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F227" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G227" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H227" s="3" t="s">
         <v>53</v>
@@ -11328,30 +11352,30 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B228" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C228" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D228" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E228" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F228" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G228" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H228" s="3" t="s">
         <v>53</v>
@@ -11360,30 +11384,30 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B229" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C229" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D229" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E229" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F229" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G229" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H229" s="3" t="s">
         <v>53</v>
@@ -11392,30 +11416,30 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B230" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C230" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D230" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E230" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F230" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G230" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H230" s="3" t="s">
         <v>53</v>
@@ -11424,30 +11448,30 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B231" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C231" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D231" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E231" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F231" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G231" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H231" s="3" t="s">
         <v>53</v>
@@ -11456,30 +11480,30 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B232" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C232" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D232" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E232" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F232" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G232" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H232" s="3" t="s">
         <v>53</v>
@@ -11488,30 +11512,30 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B233" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C233" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D233" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E233" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F233" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G233" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H233" s="3" t="s">
         <v>53</v>
@@ -11520,30 +11544,30 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B234" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C234" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D234" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E234" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F234" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G234" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H234" s="3" t="s">
         <v>53</v>
@@ -11552,30 +11576,30 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B235" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C235" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D235" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E235" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F235" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G235" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>53</v>
@@ -11584,30 +11608,30 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B236" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C236" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D236" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E236" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F236" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G236" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H236" s="3" t="s">
         <v>53</v>
@@ -11616,30 +11640,30 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B237" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C237" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D237" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E237" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F237" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G237" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>53</v>
@@ -11648,30 +11672,30 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B238" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C238" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D238" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E238" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F238" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G238" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>53</v>
@@ -11680,7 +11704,7 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -11688,10 +11712,10 @@
         <v>889</v>
       </c>
       <c r="B239" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C239" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D239" t="s">
         <v>890</v>
@@ -11700,7 +11724,7 @@
         <v>891</v>
       </c>
       <c r="F239" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G239" t="s">
         <v>892</v>
@@ -11712,7 +11736,7 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
@@ -11720,10 +11744,10 @@
         <v>893</v>
       </c>
       <c r="B240" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C240" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D240" t="s">
         <v>894</v>
@@ -11732,7 +11756,7 @@
         <v>895</v>
       </c>
       <c r="F240" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G240" t="s">
         <v>896</v>
@@ -11744,7 +11768,7 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -11752,10 +11776,10 @@
         <v>897</v>
       </c>
       <c r="B241" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C241" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D241" t="s">
         <v>898</v>
@@ -11764,7 +11788,7 @@
         <v>899</v>
       </c>
       <c r="F241" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G241" t="s">
         <v>900</v>
@@ -11776,7 +11800,7 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -11784,10 +11808,10 @@
         <v>901</v>
       </c>
       <c r="B242" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C242" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D242" t="s">
         <v>902</v>
@@ -11796,7 +11820,7 @@
         <v>903</v>
       </c>
       <c r="F242" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G242" t="s">
         <v>904</v>
@@ -11808,7 +11832,7 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -11816,10 +11840,10 @@
         <v>905</v>
       </c>
       <c r="B243" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C243" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D243" t="s">
         <v>906</v>
@@ -11828,7 +11852,7 @@
         <v>907</v>
       </c>
       <c r="F243" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G243" t="s">
         <v>908</v>
@@ -11840,7 +11864,7 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
@@ -11848,10 +11872,10 @@
         <v>909</v>
       </c>
       <c r="B244" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C244" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D244" t="s">
         <v>910</v>
@@ -11860,7 +11884,7 @@
         <v>911</v>
       </c>
       <c r="F244" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G244" t="s">
         <v>912</v>
@@ -11872,7 +11896,7 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
@@ -11880,10 +11904,10 @@
         <v>913</v>
       </c>
       <c r="B245" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C245" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D245" t="s">
         <v>914</v>
@@ -11892,7 +11916,7 @@
         <v>915</v>
       </c>
       <c r="F245" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G245" t="s">
         <v>916</v>
@@ -11904,7 +11928,7 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
@@ -11912,10 +11936,10 @@
         <v>917</v>
       </c>
       <c r="B246" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C246" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D246" t="s">
         <v>918</v>
@@ -11924,7 +11948,7 @@
         <v>919</v>
       </c>
       <c r="F246" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G246" t="s">
         <v>920</v>
@@ -11936,7 +11960,7 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
@@ -11944,10 +11968,10 @@
         <v>921</v>
       </c>
       <c r="B247" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C247" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D247" t="s">
         <v>922</v>
@@ -11956,7 +11980,7 @@
         <v>923</v>
       </c>
       <c r="F247" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G247" t="s">
         <v>924</v>
@@ -11968,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
@@ -11976,10 +12000,10 @@
         <v>925</v>
       </c>
       <c r="B248" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C248" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D248" t="s">
         <v>926</v>
@@ -11988,7 +12012,7 @@
         <v>927</v>
       </c>
       <c r="F248" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G248" t="s">
         <v>928</v>
@@ -12000,7 +12024,7 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
@@ -12008,10 +12032,10 @@
         <v>929</v>
       </c>
       <c r="B249" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C249" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D249" t="s">
         <v>930</v>
@@ -12020,7 +12044,7 @@
         <v>931</v>
       </c>
       <c r="F249" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G249" t="s">
         <v>932</v>
@@ -12032,7 +12056,7 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
@@ -12040,10 +12064,10 @@
         <v>933</v>
       </c>
       <c r="B250" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C250" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D250" t="s">
         <v>934</v>
@@ -12052,7 +12076,7 @@
         <v>935</v>
       </c>
       <c r="F250" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G250" t="s">
         <v>936</v>
@@ -12064,7 +12088,7 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
@@ -12072,10 +12096,10 @@
         <v>937</v>
       </c>
       <c r="B251" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C251" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D251" t="s">
         <v>938</v>
@@ -12084,7 +12108,7 @@
         <v>939</v>
       </c>
       <c r="F251" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G251" t="s">
         <v>940</v>
@@ -12096,7 +12120,7 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
@@ -12125,7 +12149,7 @@
         <v>53</v>
       </c>
       <c r="I252">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J252" t="s">
         <v>948</v>
@@ -13280,12 +13304,12 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B289" t="s">
         <v>1066</v>
@@ -13294,16 +13318,16 @@
         <v>1067</v>
       </c>
       <c r="D289" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="E289" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F289" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G289" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H289" s="3" t="s">
         <v>53</v>
@@ -13312,12 +13336,12 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B290" t="s">
         <v>1066</v>
@@ -13326,16 +13350,16 @@
         <v>1067</v>
       </c>
       <c r="D290" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E290" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F290" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="G290" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>53</v>
@@ -13344,12 +13368,12 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B291" t="s">
         <v>1066</v>
@@ -13358,16 +13382,16 @@
         <v>1067</v>
       </c>
       <c r="D291" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="E291" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F291" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G291" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H291" s="3" t="s">
         <v>53</v>
@@ -13376,12 +13400,12 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B292" t="s">
         <v>1066</v>
@@ -13390,7 +13414,7 @@
         <v>1067</v>
       </c>
       <c r="D292" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="E292" t="s">
         <v>1069</v>
@@ -13399,7 +13423,7 @@
         <v>1070</v>
       </c>
       <c r="G292" t="s">
-        <v>1071</v>
+        <v>1120</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>53</v>
@@ -13408,12 +13432,12 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B293" t="s">
         <v>1066</v>
@@ -13422,7 +13446,7 @@
         <v>1067</v>
       </c>
       <c r="D293" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E293" t="s">
         <v>1074</v>
@@ -13431,7 +13455,7 @@
         <v>1075</v>
       </c>
       <c r="G293" t="s">
-        <v>1076</v>
+        <v>1123</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>53</v>
@@ -13440,12 +13464,12 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B294" t="s">
         <v>1066</v>
@@ -13454,7 +13478,7 @@
         <v>1067</v>
       </c>
       <c r="D294" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E294" t="s">
         <v>1079</v>
@@ -13463,7 +13487,7 @@
         <v>1080</v>
       </c>
       <c r="G294" t="s">
-        <v>1081</v>
+        <v>1126</v>
       </c>
       <c r="H294" s="3" t="s">
         <v>53</v>
@@ -13472,12 +13496,12 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B295" t="s">
         <v>1066</v>
@@ -13486,7 +13510,7 @@
         <v>1067</v>
       </c>
       <c r="D295" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="E295" t="s">
         <v>1084</v>
@@ -13495,7 +13519,7 @@
         <v>1085</v>
       </c>
       <c r="G295" t="s">
-        <v>1086</v>
+        <v>1129</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>53</v>
@@ -13504,12 +13528,12 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="B296" t="s">
         <v>1066</v>
@@ -13518,7 +13542,7 @@
         <v>1067</v>
       </c>
       <c r="D296" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="E296" t="s">
         <v>1089</v>
@@ -13527,7 +13551,7 @@
         <v>1090</v>
       </c>
       <c r="G296" t="s">
-        <v>1091</v>
+        <v>1132</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>53</v>
@@ -13536,12 +13560,12 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="B297" t="s">
         <v>1066</v>
@@ -13550,7 +13574,7 @@
         <v>1067</v>
       </c>
       <c r="D297" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="E297" t="s">
         <v>1094</v>
@@ -13559,7 +13583,7 @@
         <v>1095</v>
       </c>
       <c r="G297" t="s">
-        <v>1096</v>
+        <v>1135</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>53</v>
@@ -13568,12 +13592,12 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
       <c r="B298" t="s">
         <v>1066</v>
@@ -13582,7 +13606,7 @@
         <v>1067</v>
       </c>
       <c r="D298" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="E298" t="s">
         <v>1099</v>
@@ -13591,7 +13615,7 @@
         <v>1100</v>
       </c>
       <c r="G298" t="s">
-        <v>1101</v>
+        <v>1138</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>53</v>
@@ -13600,12 +13624,12 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="B299" t="s">
         <v>1066</v>
@@ -13614,16 +13638,16 @@
         <v>1067</v>
       </c>
       <c r="D299" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="E299" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F299" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G299" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>53</v>
@@ -13632,12 +13656,12 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="B300" t="s">
         <v>1066</v>
@@ -13646,16 +13670,16 @@
         <v>1067</v>
       </c>
       <c r="D300" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="E300" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F300" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="G300" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H300" s="3" t="s">
         <v>53</v>
@@ -13664,12 +13688,12 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="B301" t="s">
         <v>1066</v>
@@ -13678,16 +13702,16 @@
         <v>1067</v>
       </c>
       <c r="D301" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="E301" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F301" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G301" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>53</v>
@@ -13696,7 +13720,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>948</v>
+        <v>1102</v>
       </c>
     </row>
   </sheetData>

--- a/reports/unit-test-report.xlsx
+++ b/reports/unit-test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="1146">
   <si>
     <t>Metric</t>
   </si>
@@ -62,7 +62,7 @@
     <t>EXECUTION TIME</t>
   </si>
   <si>
-    <t>0.05 seconds</t>
+    <t>0.08 seconds</t>
   </si>
   <si>
     <t>High-speed automated execution</t>
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>7/8/2026, 10:47:57 am</t>
+    <t>7/8/2026, 11:08:38 am</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:57.378Z</t>
+    <t>2026-08-07T05:38:38.327Z</t>
   </si>
   <si>
     <t>UT-API-002</t>
@@ -188,7 +188,7 @@
     <t>token_header_2, algorithm='HS256', expiry=7200s</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:57.379Z</t>
+    <t>2026-08-07T05:38:38.329Z</t>
   </si>
   <si>
     <t>UT-API-003</t>
@@ -440,9 +440,6 @@
     <t>refresh_token_id='rt_test_29', client_ip='192.168.1.29'</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:57.380Z</t>
-  </si>
-  <si>
     <t>UT-API-030</t>
   </si>
   <si>
@@ -461,6 +458,9 @@
     <t>refresh_token_id='rt_test_31', client_ip='192.168.1.31'</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:38.330Z</t>
+  </si>
+  <si>
     <t>UT-API-032</t>
   </si>
   <si>
@@ -869,7 +869,7 @@
     <t>Subtotal=$316.25, Disc=$47.44, GST=$48.39, Total=$330.64</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:57.381Z</t>
+    <t>2026-08-07T05:38:38.331Z</t>
   </si>
   <si>
     <t>UT-API-077</t>
@@ -1136,9 +1136,6 @@
     <t>Subtotal=$2803.5, Disc=$50, GST=$495.63, Total=$3386.81</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:57.382Z</t>
-  </si>
-  <si>
     <t>UT-API-099</t>
   </si>
   <si>
@@ -1283,6 +1280,9 @@
     <t>Subtotal=$1312.5, Disc=$262.5, GST=$189, Total=$1291.5</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:38.332Z</t>
+  </si>
+  <si>
     <t>UT-API-111</t>
   </si>
   <si>
@@ -1436,9 +1436,6 @@
     <t>Calculated distance: 51.28 km</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:57.383Z</t>
-  </si>
-  <si>
     <t>UT-API-123</t>
   </si>
   <si>
@@ -1751,6 +1748,9 @@
     <t>Calculated distance: 75.55 km</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:38.333Z</t>
+  </si>
+  <si>
     <t>UT-API-149</t>
   </si>
   <si>
@@ -2180,9 +2180,6 @@
     <t>1650 JPY = 16.26 AUD</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:57.384Z</t>
-  </si>
-  <si>
     <t>UT-API-184</t>
   </si>
   <si>
@@ -2396,6 +2393,9 @@
     <t>Booking FSM State Transition Check #23 (PENDING -&gt; CONFIRMED)</t>
   </si>
   <si>
+    <t>2026-08-07T05:38:38.334Z</t>
+  </si>
+  <si>
     <t>UT-API-209</t>
   </si>
   <si>
@@ -2858,7 +2858,7 @@
     <t>Computed: bookings_count=124, gross_revenue=$15,750, conversion_rate=4.3%</t>
   </si>
   <si>
-    <t>2026-08-07T05:17:57.429Z</t>
+    <t>2026-08-07T05:38:38.408Z</t>
   </si>
   <si>
     <t>UT-API-252</t>
@@ -3227,7 +3227,7 @@
     <t>Standardized RFC 7807 JSON error response with code 400</t>
   </si>
   <si>
-    <t>Returned payload: { status: 400, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
+    <t>Returned payload: { status: 400, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-282</t>
@@ -3242,7 +3242,7 @@
     <t>Standardized RFC 7807 JSON error response with code 401</t>
   </si>
   <si>
-    <t>Returned payload: { status: 401, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
+    <t>Returned payload: { status: 401, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-283</t>
@@ -3257,7 +3257,7 @@
     <t>Standardized RFC 7807 JSON error response with code 403</t>
   </si>
   <si>
-    <t>Returned payload: { status: 403, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
+    <t>Returned payload: { status: 403, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-284</t>
@@ -3272,7 +3272,7 @@
     <t>Standardized RFC 7807 JSON error response with code 404</t>
   </si>
   <si>
-    <t>Returned payload: { status: 404, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
+    <t>Returned payload: { status: 404, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-285</t>
@@ -3287,7 +3287,7 @@
     <t>Standardized RFC 7807 JSON error response with code 409</t>
   </si>
   <si>
-    <t>Returned payload: { status: 409, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
+    <t>Returned payload: { status: 409, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-286</t>
@@ -3302,7 +3302,7 @@
     <t>Standardized RFC 7807 JSON error response with code 422</t>
   </si>
   <si>
-    <t>Returned payload: { status: 422, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
+    <t>Returned payload: { status: 422, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-287</t>
@@ -3317,10 +3317,7 @@
     <t>Standardized RFC 7807 JSON error response with code 429</t>
   </si>
   <si>
-    <t>Returned payload: { status: 429, error: 'Handled', timestamp: '2026-08-07T05:17:57.429Z' }</t>
-  </si>
-  <si>
-    <t>2026-08-07T05:17:57.430Z</t>
+    <t>Returned payload: { status: 429, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-288</t>
@@ -3335,7 +3332,7 @@
     <t>Standardized RFC 7807 JSON error response with code 500</t>
   </si>
   <si>
-    <t>Returned payload: { status: 500, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+    <t>Returned payload: { status: 500, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-289</t>
@@ -3350,7 +3347,7 @@
     <t>Standardized RFC 7807 JSON error response with code 502</t>
   </si>
   <si>
-    <t>Returned payload: { status: 502, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+    <t>Returned payload: { status: 502, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-290</t>
@@ -3365,7 +3362,7 @@
     <t>Standardized RFC 7807 JSON error response with code 503</t>
   </si>
   <si>
-    <t>Returned payload: { status: 503, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+    <t>Returned payload: { status: 503, error: 'Handled', timestamp: '2026-08-07T05:38:38.408Z' }</t>
   </si>
   <si>
     <t>UT-API-291</t>
@@ -3374,25 +3371,22 @@
     <t>Error Middleware Response Contract Validation #11 (HTTP 400)</t>
   </si>
   <si>
-    <t>Returned payload: { status: 400, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
-  </si>
-  <si>
     <t>UT-API-292</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #12 (HTTP 401)</t>
   </si>
   <si>
-    <t>Returned payload: { status: 401, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
-  </si>
-  <si>
     <t>UT-API-293</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #13 (HTTP 403)</t>
   </si>
   <si>
-    <t>Returned payload: { status: 403, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+    <t>Returned payload: { status: 403, error: 'Handled', timestamp: '2026-08-07T05:38:38.409Z' }</t>
+  </si>
+  <si>
+    <t>2026-08-07T05:38:38.409Z</t>
   </si>
   <si>
     <t>UT-API-294</t>
@@ -3401,7 +3395,7 @@
     <t>Error Middleware Response Contract Validation #14 (HTTP 404)</t>
   </si>
   <si>
-    <t>Returned payload: { status: 404, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+    <t>Returned payload: { status: 404, error: 'Handled', timestamp: '2026-08-07T05:38:38.409Z' }</t>
   </si>
   <si>
     <t>UT-API-295</t>
@@ -3410,7 +3404,7 @@
     <t>Error Middleware Response Contract Validation #15 (HTTP 409)</t>
   </si>
   <si>
-    <t>Returned payload: { status: 409, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+    <t>Returned payload: { status: 409, error: 'Handled', timestamp: '2026-08-07T05:38:38.409Z' }</t>
   </si>
   <si>
     <t>UT-API-296</t>
@@ -3419,7 +3413,7 @@
     <t>Error Middleware Response Contract Validation #16 (HTTP 422)</t>
   </si>
   <si>
-    <t>Returned payload: { status: 422, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+    <t>Returned payload: { status: 422, error: 'Handled', timestamp: '2026-08-07T05:38:38.409Z' }</t>
   </si>
   <si>
     <t>UT-API-297</t>
@@ -3428,7 +3422,7 @@
     <t>Error Middleware Response Contract Validation #17 (HTTP 429)</t>
   </si>
   <si>
-    <t>Returned payload: { status: 429, error: 'Handled', timestamp: '2026-08-07T05:17:57.430Z' }</t>
+    <t>Returned payload: { status: 429, error: 'Handled', timestamp: '2026-08-07T05:38:38.409Z' }</t>
   </si>
   <si>
     <t>UT-API-298</t>
@@ -3437,16 +3431,25 @@
     <t>Error Middleware Response Contract Validation #18 (HTTP 500)</t>
   </si>
   <si>
+    <t>Returned payload: { status: 500, error: 'Handled', timestamp: '2026-08-07T05:38:38.409Z' }</t>
+  </si>
+  <si>
     <t>UT-API-299</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #19 (HTTP 502)</t>
   </si>
   <si>
+    <t>Returned payload: { status: 502, error: 'Handled', timestamp: '2026-08-07T05:38:38.409Z' }</t>
+  </si>
+  <si>
     <t>UT-API-300</t>
   </si>
   <si>
     <t>Error Middleware Response Contract Validation #20 (HTTP 503)</t>
+  </si>
+  <si>
+    <t>Returned payload: { status: 503, error: 'Handled', timestamp: '2026-08-07T05:38:38.409Z' }</t>
   </si>
 </sst>
 </file>
@@ -5048,12 +5051,12 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
@@ -5062,10 +5065,10 @@
         <v>48</v>
       </c>
       <c r="D31" t="s">
+        <v>143</v>
+      </c>
+      <c r="E31" t="s">
         <v>144</v>
-      </c>
-      <c r="E31" t="s">
-        <v>145</v>
       </c>
       <c r="F31" t="s">
         <v>116</v>
@@ -5080,12 +5083,12 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
@@ -5094,10 +5097,10 @@
         <v>48</v>
       </c>
       <c r="D32" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" t="s">
         <v>147</v>
-      </c>
-      <c r="E32" t="s">
-        <v>148</v>
       </c>
       <c r="F32" t="s">
         <v>116</v>
@@ -5112,7 +5115,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -5144,7 +5147,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -5176,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -5208,7 +5211,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -5240,7 +5243,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -5272,7 +5275,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -5304,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -5336,7 +5339,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -5368,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -5400,7 +5403,7 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -5432,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -5464,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -5496,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -5528,7 +5531,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -5560,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -5592,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -5624,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -5656,7 +5659,7 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -5688,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -5720,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -5752,7 +5755,7 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -5784,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -5816,7 +5819,7 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -5848,7 +5851,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -5880,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -5912,7 +5915,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -5944,7 +5947,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5976,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -6008,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -6040,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -6072,7 +6075,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -6104,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -6136,7 +6139,7 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -6168,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -6200,7 +6203,7 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -6232,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -6264,7 +6267,7 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -6296,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -6328,7 +6331,7 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -6360,7 +6363,7 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -6392,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="J72" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -6424,7 +6427,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -6456,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -6488,7 +6491,7 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -6520,7 +6523,7 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -7256,12 +7259,12 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B100" t="s">
         <v>279</v>
@@ -7270,16 +7273,16 @@
         <v>280</v>
       </c>
       <c r="D100" t="s">
+        <v>375</v>
+      </c>
+      <c r="E100" t="s">
         <v>376</v>
-      </c>
-      <c r="E100" t="s">
-        <v>377</v>
       </c>
       <c r="F100" t="s">
         <v>283</v>
       </c>
       <c r="G100" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>53</v>
@@ -7288,12 +7291,12 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B101" t="s">
         <v>279</v>
@@ -7302,16 +7305,16 @@
         <v>280</v>
       </c>
       <c r="D101" t="s">
+        <v>379</v>
+      </c>
+      <c r="E101" t="s">
         <v>380</v>
-      </c>
-      <c r="E101" t="s">
-        <v>381</v>
       </c>
       <c r="F101" t="s">
         <v>283</v>
       </c>
       <c r="G101" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>53</v>
@@ -7320,12 +7323,12 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B102" t="s">
         <v>279</v>
@@ -7334,16 +7337,16 @@
         <v>280</v>
       </c>
       <c r="D102" t="s">
+        <v>383</v>
+      </c>
+      <c r="E102" t="s">
         <v>384</v>
-      </c>
-      <c r="E102" t="s">
-        <v>385</v>
       </c>
       <c r="F102" t="s">
         <v>283</v>
       </c>
       <c r="G102" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>53</v>
@@ -7352,12 +7355,12 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B103" t="s">
         <v>279</v>
@@ -7366,16 +7369,16 @@
         <v>280</v>
       </c>
       <c r="D103" t="s">
+        <v>387</v>
+      </c>
+      <c r="E103" t="s">
         <v>388</v>
-      </c>
-      <c r="E103" t="s">
-        <v>389</v>
       </c>
       <c r="F103" t="s">
         <v>283</v>
       </c>
       <c r="G103" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>53</v>
@@ -7384,12 +7387,12 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B104" t="s">
         <v>279</v>
@@ -7398,16 +7401,16 @@
         <v>280</v>
       </c>
       <c r="D104" t="s">
+        <v>391</v>
+      </c>
+      <c r="E104" t="s">
         <v>392</v>
-      </c>
-      <c r="E104" t="s">
-        <v>393</v>
       </c>
       <c r="F104" t="s">
         <v>283</v>
       </c>
       <c r="G104" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>53</v>
@@ -7416,12 +7419,12 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B105" t="s">
         <v>279</v>
@@ -7430,16 +7433,16 @@
         <v>280</v>
       </c>
       <c r="D105" t="s">
+        <v>395</v>
+      </c>
+      <c r="E105" t="s">
         <v>396</v>
-      </c>
-      <c r="E105" t="s">
-        <v>397</v>
       </c>
       <c r="F105" t="s">
         <v>283</v>
       </c>
       <c r="G105" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>53</v>
@@ -7448,12 +7451,12 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B106" t="s">
         <v>279</v>
@@ -7462,16 +7465,16 @@
         <v>280</v>
       </c>
       <c r="D106" t="s">
+        <v>399</v>
+      </c>
+      <c r="E106" t="s">
         <v>400</v>
-      </c>
-      <c r="E106" t="s">
-        <v>401</v>
       </c>
       <c r="F106" t="s">
         <v>283</v>
       </c>
       <c r="G106" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>53</v>
@@ -7480,12 +7483,12 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B107" t="s">
         <v>279</v>
@@ -7494,16 +7497,16 @@
         <v>280</v>
       </c>
       <c r="D107" t="s">
+        <v>403</v>
+      </c>
+      <c r="E107" t="s">
         <v>404</v>
-      </c>
-      <c r="E107" t="s">
-        <v>405</v>
       </c>
       <c r="F107" t="s">
         <v>283</v>
       </c>
       <c r="G107" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>53</v>
@@ -7512,12 +7515,12 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B108" t="s">
         <v>279</v>
@@ -7526,16 +7529,16 @@
         <v>280</v>
       </c>
       <c r="D108" t="s">
+        <v>407</v>
+      </c>
+      <c r="E108" t="s">
         <v>408</v>
-      </c>
-      <c r="E108" t="s">
-        <v>409</v>
       </c>
       <c r="F108" t="s">
         <v>283</v>
       </c>
       <c r="G108" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>53</v>
@@ -7544,12 +7547,12 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B109" t="s">
         <v>279</v>
@@ -7558,16 +7561,16 @@
         <v>280</v>
       </c>
       <c r="D109" t="s">
+        <v>411</v>
+      </c>
+      <c r="E109" t="s">
         <v>412</v>
-      </c>
-      <c r="E109" t="s">
-        <v>413</v>
       </c>
       <c r="F109" t="s">
         <v>283</v>
       </c>
       <c r="G109" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>53</v>
@@ -7576,12 +7579,12 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B110" t="s">
         <v>279</v>
@@ -7590,16 +7593,16 @@
         <v>280</v>
       </c>
       <c r="D110" t="s">
+        <v>415</v>
+      </c>
+      <c r="E110" t="s">
         <v>416</v>
-      </c>
-      <c r="E110" t="s">
-        <v>417</v>
       </c>
       <c r="F110" t="s">
         <v>283</v>
       </c>
       <c r="G110" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>53</v>
@@ -7608,12 +7611,12 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B111" t="s">
         <v>279</v>
@@ -7622,25 +7625,25 @@
         <v>280</v>
       </c>
       <c r="D111" t="s">
+        <v>419</v>
+      </c>
+      <c r="E111" t="s">
         <v>420</v>
-      </c>
-      <c r="E111" t="s">
-        <v>421</v>
       </c>
       <c r="F111" t="s">
         <v>283</v>
       </c>
       <c r="G111" t="s">
+        <v>421</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111" t="s">
         <v>422</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I111">
-        <v>1</v>
-      </c>
-      <c r="J111" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -7672,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -7704,7 +7707,7 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -7736,7 +7739,7 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -7768,7 +7771,7 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -7800,7 +7803,7 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -7832,7 +7835,7 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -7864,7 +7867,7 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -7896,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -7928,7 +7931,7 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -7960,7 +7963,7 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -7992,7 +7995,7 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -8024,12 +8027,12 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B124" t="s">
         <v>444</v>
@@ -8038,16 +8041,16 @@
         <v>445</v>
       </c>
       <c r="D124" t="s">
+        <v>475</v>
+      </c>
+      <c r="E124" t="s">
         <v>476</v>
-      </c>
-      <c r="E124" t="s">
-        <v>477</v>
       </c>
       <c r="F124" t="s">
         <v>448</v>
       </c>
       <c r="G124" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>53</v>
@@ -8056,12 +8059,12 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B125" t="s">
         <v>444</v>
@@ -8070,16 +8073,16 @@
         <v>445</v>
       </c>
       <c r="D125" t="s">
+        <v>479</v>
+      </c>
+      <c r="E125" t="s">
         <v>480</v>
-      </c>
-      <c r="E125" t="s">
-        <v>481</v>
       </c>
       <c r="F125" t="s">
         <v>448</v>
       </c>
       <c r="G125" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>53</v>
@@ -8088,12 +8091,12 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B126" t="s">
         <v>444</v>
@@ -8102,16 +8105,16 @@
         <v>445</v>
       </c>
       <c r="D126" t="s">
+        <v>483</v>
+      </c>
+      <c r="E126" t="s">
         <v>484</v>
-      </c>
-      <c r="E126" t="s">
-        <v>485</v>
       </c>
       <c r="F126" t="s">
         <v>448</v>
       </c>
       <c r="G126" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>53</v>
@@ -8120,12 +8123,12 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B127" t="s">
         <v>444</v>
@@ -8134,16 +8137,16 @@
         <v>445</v>
       </c>
       <c r="D127" t="s">
+        <v>487</v>
+      </c>
+      <c r="E127" t="s">
         <v>488</v>
-      </c>
-      <c r="E127" t="s">
-        <v>489</v>
       </c>
       <c r="F127" t="s">
         <v>448</v>
       </c>
       <c r="G127" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>53</v>
@@ -8152,12 +8155,12 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B128" t="s">
         <v>444</v>
@@ -8166,16 +8169,16 @@
         <v>445</v>
       </c>
       <c r="D128" t="s">
+        <v>491</v>
+      </c>
+      <c r="E128" t="s">
         <v>492</v>
-      </c>
-      <c r="E128" t="s">
-        <v>493</v>
       </c>
       <c r="F128" t="s">
         <v>448</v>
       </c>
       <c r="G128" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>53</v>
@@ -8184,12 +8187,12 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B129" t="s">
         <v>444</v>
@@ -8198,16 +8201,16 @@
         <v>445</v>
       </c>
       <c r="D129" t="s">
+        <v>495</v>
+      </c>
+      <c r="E129" t="s">
         <v>496</v>
-      </c>
-      <c r="E129" t="s">
-        <v>497</v>
       </c>
       <c r="F129" t="s">
         <v>448</v>
       </c>
       <c r="G129" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H129" s="3" t="s">
         <v>53</v>
@@ -8216,12 +8219,12 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B130" t="s">
         <v>444</v>
@@ -8230,16 +8233,16 @@
         <v>445</v>
       </c>
       <c r="D130" t="s">
+        <v>499</v>
+      </c>
+      <c r="E130" t="s">
         <v>500</v>
-      </c>
-      <c r="E130" t="s">
-        <v>501</v>
       </c>
       <c r="F130" t="s">
         <v>448</v>
       </c>
       <c r="G130" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>53</v>
@@ -8248,12 +8251,12 @@
         <v>1</v>
       </c>
       <c r="J130" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B131" t="s">
         <v>444</v>
@@ -8262,16 +8265,16 @@
         <v>445</v>
       </c>
       <c r="D131" t="s">
+        <v>503</v>
+      </c>
+      <c r="E131" t="s">
         <v>504</v>
-      </c>
-      <c r="E131" t="s">
-        <v>505</v>
       </c>
       <c r="F131" t="s">
         <v>448</v>
       </c>
       <c r="G131" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H131" s="3" t="s">
         <v>53</v>
@@ -8280,12 +8283,12 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B132" t="s">
         <v>444</v>
@@ -8294,16 +8297,16 @@
         <v>445</v>
       </c>
       <c r="D132" t="s">
+        <v>507</v>
+      </c>
+      <c r="E132" t="s">
         <v>508</v>
-      </c>
-      <c r="E132" t="s">
-        <v>509</v>
       </c>
       <c r="F132" t="s">
         <v>448</v>
       </c>
       <c r="G132" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>53</v>
@@ -8312,12 +8315,12 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B133" t="s">
         <v>444</v>
@@ -8326,16 +8329,16 @@
         <v>445</v>
       </c>
       <c r="D133" t="s">
+        <v>511</v>
+      </c>
+      <c r="E133" t="s">
         <v>512</v>
-      </c>
-      <c r="E133" t="s">
-        <v>513</v>
       </c>
       <c r="F133" t="s">
         <v>448</v>
       </c>
       <c r="G133" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>53</v>
@@ -8344,12 +8347,12 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B134" t="s">
         <v>444</v>
@@ -8358,16 +8361,16 @@
         <v>445</v>
       </c>
       <c r="D134" t="s">
+        <v>515</v>
+      </c>
+      <c r="E134" t="s">
         <v>516</v>
-      </c>
-      <c r="E134" t="s">
-        <v>517</v>
       </c>
       <c r="F134" t="s">
         <v>448</v>
       </c>
       <c r="G134" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>53</v>
@@ -8376,12 +8379,12 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B135" t="s">
         <v>444</v>
@@ -8390,16 +8393,16 @@
         <v>445</v>
       </c>
       <c r="D135" t="s">
+        <v>519</v>
+      </c>
+      <c r="E135" t="s">
         <v>520</v>
-      </c>
-      <c r="E135" t="s">
-        <v>521</v>
       </c>
       <c r="F135" t="s">
         <v>448</v>
       </c>
       <c r="G135" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>53</v>
@@ -8408,12 +8411,12 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B136" t="s">
         <v>444</v>
@@ -8422,16 +8425,16 @@
         <v>445</v>
       </c>
       <c r="D136" t="s">
+        <v>523</v>
+      </c>
+      <c r="E136" t="s">
         <v>524</v>
-      </c>
-      <c r="E136" t="s">
-        <v>525</v>
       </c>
       <c r="F136" t="s">
         <v>448</v>
       </c>
       <c r="G136" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>53</v>
@@ -8440,12 +8443,12 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B137" t="s">
         <v>444</v>
@@ -8454,16 +8457,16 @@
         <v>445</v>
       </c>
       <c r="D137" t="s">
+        <v>527</v>
+      </c>
+      <c r="E137" t="s">
         <v>528</v>
-      </c>
-      <c r="E137" t="s">
-        <v>529</v>
       </c>
       <c r="F137" t="s">
         <v>448</v>
       </c>
       <c r="G137" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H137" s="3" t="s">
         <v>53</v>
@@ -8472,12 +8475,12 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B138" t="s">
         <v>444</v>
@@ -8486,16 +8489,16 @@
         <v>445</v>
       </c>
       <c r="D138" t="s">
+        <v>531</v>
+      </c>
+      <c r="E138" t="s">
         <v>532</v>
-      </c>
-      <c r="E138" t="s">
-        <v>533</v>
       </c>
       <c r="F138" t="s">
         <v>448</v>
       </c>
       <c r="G138" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>53</v>
@@ -8504,12 +8507,12 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B139" t="s">
         <v>444</v>
@@ -8518,16 +8521,16 @@
         <v>445</v>
       </c>
       <c r="D139" t="s">
+        <v>535</v>
+      </c>
+      <c r="E139" t="s">
         <v>536</v>
-      </c>
-      <c r="E139" t="s">
-        <v>537</v>
       </c>
       <c r="F139" t="s">
         <v>448</v>
       </c>
       <c r="G139" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>53</v>
@@ -8536,12 +8539,12 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B140" t="s">
         <v>444</v>
@@ -8550,16 +8553,16 @@
         <v>445</v>
       </c>
       <c r="D140" t="s">
+        <v>539</v>
+      </c>
+      <c r="E140" t="s">
         <v>540</v>
-      </c>
-      <c r="E140" t="s">
-        <v>541</v>
       </c>
       <c r="F140" t="s">
         <v>448</v>
       </c>
       <c r="G140" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H140" s="3" t="s">
         <v>53</v>
@@ -8568,12 +8571,12 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B141" t="s">
         <v>444</v>
@@ -8582,16 +8585,16 @@
         <v>445</v>
       </c>
       <c r="D141" t="s">
+        <v>543</v>
+      </c>
+      <c r="E141" t="s">
         <v>544</v>
-      </c>
-      <c r="E141" t="s">
-        <v>545</v>
       </c>
       <c r="F141" t="s">
         <v>448</v>
       </c>
       <c r="G141" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>53</v>
@@ -8600,12 +8603,12 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B142" t="s">
         <v>444</v>
@@ -8614,16 +8617,16 @@
         <v>445</v>
       </c>
       <c r="D142" t="s">
+        <v>547</v>
+      </c>
+      <c r="E142" t="s">
         <v>548</v>
-      </c>
-      <c r="E142" t="s">
-        <v>549</v>
       </c>
       <c r="F142" t="s">
         <v>448</v>
       </c>
       <c r="G142" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H142" s="3" t="s">
         <v>53</v>
@@ -8632,12 +8635,12 @@
         <v>1</v>
       </c>
       <c r="J142" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B143" t="s">
         <v>444</v>
@@ -8646,16 +8649,16 @@
         <v>445</v>
       </c>
       <c r="D143" t="s">
+        <v>551</v>
+      </c>
+      <c r="E143" t="s">
         <v>552</v>
-      </c>
-      <c r="E143" t="s">
-        <v>553</v>
       </c>
       <c r="F143" t="s">
         <v>448</v>
       </c>
       <c r="G143" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H143" s="3" t="s">
         <v>53</v>
@@ -8664,12 +8667,12 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B144" t="s">
         <v>444</v>
@@ -8678,16 +8681,16 @@
         <v>445</v>
       </c>
       <c r="D144" t="s">
+        <v>555</v>
+      </c>
+      <c r="E144" t="s">
         <v>556</v>
-      </c>
-      <c r="E144" t="s">
-        <v>557</v>
       </c>
       <c r="F144" t="s">
         <v>448</v>
       </c>
       <c r="G144" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H144" s="3" t="s">
         <v>53</v>
@@ -8696,12 +8699,12 @@
         <v>1</v>
       </c>
       <c r="J144" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B145" t="s">
         <v>444</v>
@@ -8710,16 +8713,16 @@
         <v>445</v>
       </c>
       <c r="D145" t="s">
+        <v>559</v>
+      </c>
+      <c r="E145" t="s">
         <v>560</v>
-      </c>
-      <c r="E145" t="s">
-        <v>561</v>
       </c>
       <c r="F145" t="s">
         <v>448</v>
       </c>
       <c r="G145" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H145" s="3" t="s">
         <v>53</v>
@@ -8728,12 +8731,12 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B146" t="s">
         <v>444</v>
@@ -8742,16 +8745,16 @@
         <v>445</v>
       </c>
       <c r="D146" t="s">
+        <v>563</v>
+      </c>
+      <c r="E146" t="s">
         <v>564</v>
-      </c>
-      <c r="E146" t="s">
-        <v>565</v>
       </c>
       <c r="F146" t="s">
         <v>448</v>
       </c>
       <c r="G146" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H146" s="3" t="s">
         <v>53</v>
@@ -8760,12 +8763,12 @@
         <v>1</v>
       </c>
       <c r="J146" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B147" t="s">
         <v>444</v>
@@ -8774,16 +8777,16 @@
         <v>445</v>
       </c>
       <c r="D147" t="s">
+        <v>567</v>
+      </c>
+      <c r="E147" t="s">
         <v>568</v>
-      </c>
-      <c r="E147" t="s">
-        <v>569</v>
       </c>
       <c r="F147" t="s">
         <v>448</v>
       </c>
       <c r="G147" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H147" s="3" t="s">
         <v>53</v>
@@ -8792,12 +8795,12 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B148" t="s">
         <v>444</v>
@@ -8806,16 +8809,16 @@
         <v>445</v>
       </c>
       <c r="D148" t="s">
+        <v>571</v>
+      </c>
+      <c r="E148" t="s">
         <v>572</v>
-      </c>
-      <c r="E148" t="s">
-        <v>573</v>
       </c>
       <c r="F148" t="s">
         <v>448</v>
       </c>
       <c r="G148" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H148" s="3" t="s">
         <v>53</v>
@@ -8824,12 +8827,12 @@
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B149" t="s">
         <v>444</v>
@@ -8838,25 +8841,25 @@
         <v>445</v>
       </c>
       <c r="D149" t="s">
+        <v>575</v>
+      </c>
+      <c r="E149" t="s">
         <v>576</v>
-      </c>
-      <c r="E149" t="s">
-        <v>577</v>
       </c>
       <c r="F149" t="s">
         <v>448</v>
       </c>
       <c r="G149" t="s">
+        <v>577</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149" t="s">
         <v>578</v>
-      </c>
-      <c r="H149" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I149">
-        <v>1</v>
-      </c>
-      <c r="J149" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -8888,7 +8891,7 @@
         <v>1</v>
       </c>
       <c r="J150" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -8920,7 +8923,7 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -8952,7 +8955,7 @@
         <v>1</v>
       </c>
       <c r="J152" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -8984,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -9016,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="J154" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -9048,7 +9051,7 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -9080,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -9112,7 +9115,7 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -9144,7 +9147,7 @@
         <v>1</v>
       </c>
       <c r="J158" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -9176,7 +9179,7 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -9208,7 +9211,7 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -9240,7 +9243,7 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -9272,7 +9275,7 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -9304,7 +9307,7 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -9336,7 +9339,7 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -9368,7 +9371,7 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -9400,7 +9403,7 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -9432,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -9464,7 +9467,7 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -9496,7 +9499,7 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -9528,7 +9531,7 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -9560,7 +9563,7 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -9592,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -9624,7 +9627,7 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -9656,7 +9659,7 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -9688,7 +9691,7 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -9720,7 +9723,7 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -9752,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="J177" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -9784,7 +9787,7 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -9816,7 +9819,7 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -9848,7 +9851,7 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -9880,7 +9883,7 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -9912,7 +9915,7 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -9944,7 +9947,7 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>474</v>
+        <v>578</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -9976,12 +9979,12 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B185" t="s">
         <v>588</v>
@@ -9990,16 +9993,16 @@
         <v>589</v>
       </c>
       <c r="D185" t="s">
+        <v>723</v>
+      </c>
+      <c r="E185" t="s">
         <v>724</v>
-      </c>
-      <c r="E185" t="s">
-        <v>725</v>
       </c>
       <c r="F185" t="s">
         <v>592</v>
       </c>
       <c r="G185" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>53</v>
@@ -10008,12 +10011,12 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B186" t="s">
         <v>588</v>
@@ -10022,16 +10025,16 @@
         <v>589</v>
       </c>
       <c r="D186" t="s">
+        <v>727</v>
+      </c>
+      <c r="E186" t="s">
         <v>728</v>
-      </c>
-      <c r="E186" t="s">
-        <v>729</v>
       </c>
       <c r="F186" t="s">
         <v>592</v>
       </c>
       <c r="G186" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>53</v>
@@ -10040,31 +10043,31 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>730</v>
+      </c>
+      <c r="B187" t="s">
         <v>731</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
         <v>732</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
         <v>733</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>734</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>735</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>736</v>
       </c>
-      <c r="G187" t="s">
-        <v>737</v>
-      </c>
       <c r="H187" s="3" t="s">
         <v>53</v>
       </c>
@@ -10072,31 +10075,31 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>737</v>
+      </c>
+      <c r="B188" t="s">
+        <v>731</v>
+      </c>
+      <c r="C188" t="s">
+        <v>732</v>
+      </c>
+      <c r="D188" t="s">
         <v>738</v>
       </c>
-      <c r="B188" t="s">
-        <v>732</v>
-      </c>
-      <c r="C188" t="s">
-        <v>733</v>
-      </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>739</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
+        <v>735</v>
+      </c>
+      <c r="G188" t="s">
         <v>740</v>
       </c>
-      <c r="F188" t="s">
-        <v>736</v>
-      </c>
-      <c r="G188" t="s">
-        <v>741</v>
-      </c>
       <c r="H188" s="3" t="s">
         <v>53</v>
       </c>
@@ -10104,31 +10107,31 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>741</v>
+      </c>
+      <c r="B189" t="s">
+        <v>731</v>
+      </c>
+      <c r="C189" t="s">
+        <v>732</v>
+      </c>
+      <c r="D189" t="s">
         <v>742</v>
       </c>
-      <c r="B189" t="s">
-        <v>732</v>
-      </c>
-      <c r="C189" t="s">
-        <v>733</v>
-      </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>743</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
+        <v>735</v>
+      </c>
+      <c r="G189" t="s">
         <v>744</v>
       </c>
-      <c r="F189" t="s">
-        <v>736</v>
-      </c>
-      <c r="G189" t="s">
-        <v>745</v>
-      </c>
       <c r="H189" s="3" t="s">
         <v>53</v>
       </c>
@@ -10136,31 +10139,31 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>745</v>
+      </c>
+      <c r="B190" t="s">
+        <v>731</v>
+      </c>
+      <c r="C190" t="s">
+        <v>732</v>
+      </c>
+      <c r="D190" t="s">
         <v>746</v>
       </c>
-      <c r="B190" t="s">
-        <v>732</v>
-      </c>
-      <c r="C190" t="s">
-        <v>733</v>
-      </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
         <v>747</v>
       </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
+        <v>735</v>
+      </c>
+      <c r="G190" t="s">
         <v>748</v>
       </c>
-      <c r="F190" t="s">
-        <v>736</v>
-      </c>
-      <c r="G190" t="s">
-        <v>749</v>
-      </c>
       <c r="H190" s="3" t="s">
         <v>53</v>
       </c>
@@ -10168,31 +10171,31 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>749</v>
+      </c>
+      <c r="B191" t="s">
+        <v>731</v>
+      </c>
+      <c r="C191" t="s">
+        <v>732</v>
+      </c>
+      <c r="D191" t="s">
         <v>750</v>
       </c>
-      <c r="B191" t="s">
-        <v>732</v>
-      </c>
-      <c r="C191" t="s">
-        <v>733</v>
-      </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
         <v>751</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
+        <v>735</v>
+      </c>
+      <c r="G191" t="s">
         <v>752</v>
       </c>
-      <c r="F191" t="s">
-        <v>736</v>
-      </c>
-      <c r="G191" t="s">
-        <v>753</v>
-      </c>
       <c r="H191" s="3" t="s">
         <v>53</v>
       </c>
@@ -10200,31 +10203,31 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>753</v>
+      </c>
+      <c r="B192" t="s">
+        <v>731</v>
+      </c>
+      <c r="C192" t="s">
+        <v>732</v>
+      </c>
+      <c r="D192" t="s">
         <v>754</v>
       </c>
-      <c r="B192" t="s">
-        <v>732</v>
-      </c>
-      <c r="C192" t="s">
-        <v>733</v>
-      </c>
-      <c r="D192" t="s">
+      <c r="E192" t="s">
         <v>755</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
+        <v>735</v>
+      </c>
+      <c r="G192" t="s">
         <v>756</v>
       </c>
-      <c r="F192" t="s">
-        <v>736</v>
-      </c>
-      <c r="G192" t="s">
-        <v>757</v>
-      </c>
       <c r="H192" s="3" t="s">
         <v>53</v>
       </c>
@@ -10232,31 +10235,31 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>757</v>
+      </c>
+      <c r="B193" t="s">
+        <v>731</v>
+      </c>
+      <c r="C193" t="s">
+        <v>732</v>
+      </c>
+      <c r="D193" t="s">
         <v>758</v>
       </c>
-      <c r="B193" t="s">
-        <v>732</v>
-      </c>
-      <c r="C193" t="s">
-        <v>733</v>
-      </c>
-      <c r="D193" t="s">
+      <c r="E193" t="s">
         <v>759</v>
       </c>
-      <c r="E193" t="s">
+      <c r="F193" t="s">
+        <v>735</v>
+      </c>
+      <c r="G193" t="s">
         <v>760</v>
       </c>
-      <c r="F193" t="s">
-        <v>736</v>
-      </c>
-      <c r="G193" t="s">
-        <v>761</v>
-      </c>
       <c r="H193" s="3" t="s">
         <v>53</v>
       </c>
@@ -10264,31 +10267,31 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>761</v>
+      </c>
+      <c r="B194" t="s">
+        <v>731</v>
+      </c>
+      <c r="C194" t="s">
+        <v>732</v>
+      </c>
+      <c r="D194" t="s">
         <v>762</v>
       </c>
-      <c r="B194" t="s">
-        <v>732</v>
-      </c>
-      <c r="C194" t="s">
-        <v>733</v>
-      </c>
-      <c r="D194" t="s">
-        <v>763</v>
-      </c>
       <c r="E194" t="s">
+        <v>734</v>
+      </c>
+      <c r="F194" t="s">
         <v>735</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>736</v>
       </c>
-      <c r="G194" t="s">
-        <v>737</v>
-      </c>
       <c r="H194" s="3" t="s">
         <v>53</v>
       </c>
@@ -10296,31 +10299,31 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>763</v>
+      </c>
+      <c r="B195" t="s">
+        <v>731</v>
+      </c>
+      <c r="C195" t="s">
+        <v>732</v>
+      </c>
+      <c r="D195" t="s">
         <v>764</v>
       </c>
-      <c r="B195" t="s">
-        <v>732</v>
-      </c>
-      <c r="C195" t="s">
-        <v>733</v>
-      </c>
-      <c r="D195" t="s">
-        <v>765</v>
-      </c>
       <c r="E195" t="s">
+        <v>739</v>
+      </c>
+      <c r="F195" t="s">
+        <v>735</v>
+      </c>
+      <c r="G195" t="s">
         <v>740</v>
       </c>
-      <c r="F195" t="s">
-        <v>736</v>
-      </c>
-      <c r="G195" t="s">
-        <v>741</v>
-      </c>
       <c r="H195" s="3" t="s">
         <v>53</v>
       </c>
@@ -10328,31 +10331,31 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>765</v>
+      </c>
+      <c r="B196" t="s">
+        <v>731</v>
+      </c>
+      <c r="C196" t="s">
+        <v>732</v>
+      </c>
+      <c r="D196" t="s">
         <v>766</v>
       </c>
-      <c r="B196" t="s">
-        <v>732</v>
-      </c>
-      <c r="C196" t="s">
-        <v>733</v>
-      </c>
-      <c r="D196" t="s">
-        <v>767</v>
-      </c>
       <c r="E196" t="s">
+        <v>743</v>
+      </c>
+      <c r="F196" t="s">
+        <v>735</v>
+      </c>
+      <c r="G196" t="s">
         <v>744</v>
       </c>
-      <c r="F196" t="s">
-        <v>736</v>
-      </c>
-      <c r="G196" t="s">
-        <v>745</v>
-      </c>
       <c r="H196" s="3" t="s">
         <v>53</v>
       </c>
@@ -10360,31 +10363,31 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>767</v>
+      </c>
+      <c r="B197" t="s">
+        <v>731</v>
+      </c>
+      <c r="C197" t="s">
+        <v>732</v>
+      </c>
+      <c r="D197" t="s">
         <v>768</v>
       </c>
-      <c r="B197" t="s">
-        <v>732</v>
-      </c>
-      <c r="C197" t="s">
-        <v>733</v>
-      </c>
-      <c r="D197" t="s">
-        <v>769</v>
-      </c>
       <c r="E197" t="s">
+        <v>747</v>
+      </c>
+      <c r="F197" t="s">
+        <v>735</v>
+      </c>
+      <c r="G197" t="s">
         <v>748</v>
       </c>
-      <c r="F197" t="s">
-        <v>736</v>
-      </c>
-      <c r="G197" t="s">
-        <v>749</v>
-      </c>
       <c r="H197" s="3" t="s">
         <v>53</v>
       </c>
@@ -10392,31 +10395,31 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>769</v>
+      </c>
+      <c r="B198" t="s">
+        <v>731</v>
+      </c>
+      <c r="C198" t="s">
+        <v>732</v>
+      </c>
+      <c r="D198" t="s">
         <v>770</v>
       </c>
-      <c r="B198" t="s">
-        <v>732</v>
-      </c>
-      <c r="C198" t="s">
-        <v>733</v>
-      </c>
-      <c r="D198" t="s">
-        <v>771</v>
-      </c>
       <c r="E198" t="s">
+        <v>751</v>
+      </c>
+      <c r="F198" t="s">
+        <v>735</v>
+      </c>
+      <c r="G198" t="s">
         <v>752</v>
       </c>
-      <c r="F198" t="s">
-        <v>736</v>
-      </c>
-      <c r="G198" t="s">
-        <v>753</v>
-      </c>
       <c r="H198" s="3" t="s">
         <v>53</v>
       </c>
@@ -10424,31 +10427,31 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>771</v>
+      </c>
+      <c r="B199" t="s">
+        <v>731</v>
+      </c>
+      <c r="C199" t="s">
+        <v>732</v>
+      </c>
+      <c r="D199" t="s">
         <v>772</v>
       </c>
-      <c r="B199" t="s">
-        <v>732</v>
-      </c>
-      <c r="C199" t="s">
-        <v>733</v>
-      </c>
-      <c r="D199" t="s">
-        <v>773</v>
-      </c>
       <c r="E199" t="s">
+        <v>755</v>
+      </c>
+      <c r="F199" t="s">
+        <v>735</v>
+      </c>
+      <c r="G199" t="s">
         <v>756</v>
       </c>
-      <c r="F199" t="s">
-        <v>736</v>
-      </c>
-      <c r="G199" t="s">
-        <v>757</v>
-      </c>
       <c r="H199" s="3" t="s">
         <v>53</v>
       </c>
@@ -10456,31 +10459,31 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>773</v>
+      </c>
+      <c r="B200" t="s">
+        <v>731</v>
+      </c>
+      <c r="C200" t="s">
+        <v>732</v>
+      </c>
+      <c r="D200" t="s">
         <v>774</v>
       </c>
-      <c r="B200" t="s">
-        <v>732</v>
-      </c>
-      <c r="C200" t="s">
-        <v>733</v>
-      </c>
-      <c r="D200" t="s">
-        <v>775</v>
-      </c>
       <c r="E200" t="s">
+        <v>759</v>
+      </c>
+      <c r="F200" t="s">
+        <v>735</v>
+      </c>
+      <c r="G200" t="s">
         <v>760</v>
       </c>
-      <c r="F200" t="s">
-        <v>736</v>
-      </c>
-      <c r="G200" t="s">
-        <v>761</v>
-      </c>
       <c r="H200" s="3" t="s">
         <v>53</v>
       </c>
@@ -10488,31 +10491,31 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>775</v>
+      </c>
+      <c r="B201" t="s">
+        <v>731</v>
+      </c>
+      <c r="C201" t="s">
+        <v>732</v>
+      </c>
+      <c r="D201" t="s">
         <v>776</v>
       </c>
-      <c r="B201" t="s">
-        <v>732</v>
-      </c>
-      <c r="C201" t="s">
-        <v>733</v>
-      </c>
-      <c r="D201" t="s">
-        <v>777</v>
-      </c>
       <c r="E201" t="s">
+        <v>734</v>
+      </c>
+      <c r="F201" t="s">
         <v>735</v>
       </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
         <v>736</v>
       </c>
-      <c r="G201" t="s">
-        <v>737</v>
-      </c>
       <c r="H201" s="3" t="s">
         <v>53</v>
       </c>
@@ -10520,31 +10523,31 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>777</v>
+      </c>
+      <c r="B202" t="s">
+        <v>731</v>
+      </c>
+      <c r="C202" t="s">
+        <v>732</v>
+      </c>
+      <c r="D202" t="s">
         <v>778</v>
       </c>
-      <c r="B202" t="s">
-        <v>732</v>
-      </c>
-      <c r="C202" t="s">
-        <v>733</v>
-      </c>
-      <c r="D202" t="s">
-        <v>779</v>
-      </c>
       <c r="E202" t="s">
+        <v>739</v>
+      </c>
+      <c r="F202" t="s">
+        <v>735</v>
+      </c>
+      <c r="G202" t="s">
         <v>740</v>
       </c>
-      <c r="F202" t="s">
-        <v>736</v>
-      </c>
-      <c r="G202" t="s">
-        <v>741</v>
-      </c>
       <c r="H202" s="3" t="s">
         <v>53</v>
       </c>
@@ -10552,31 +10555,31 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>779</v>
+      </c>
+      <c r="B203" t="s">
+        <v>731</v>
+      </c>
+      <c r="C203" t="s">
+        <v>732</v>
+      </c>
+      <c r="D203" t="s">
         <v>780</v>
       </c>
-      <c r="B203" t="s">
-        <v>732</v>
-      </c>
-      <c r="C203" t="s">
-        <v>733</v>
-      </c>
-      <c r="D203" t="s">
-        <v>781</v>
-      </c>
       <c r="E203" t="s">
+        <v>743</v>
+      </c>
+      <c r="F203" t="s">
+        <v>735</v>
+      </c>
+      <c r="G203" t="s">
         <v>744</v>
       </c>
-      <c r="F203" t="s">
-        <v>736</v>
-      </c>
-      <c r="G203" t="s">
-        <v>745</v>
-      </c>
       <c r="H203" s="3" t="s">
         <v>53</v>
       </c>
@@ -10584,31 +10587,31 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>781</v>
+      </c>
+      <c r="B204" t="s">
+        <v>731</v>
+      </c>
+      <c r="C204" t="s">
+        <v>732</v>
+      </c>
+      <c r="D204" t="s">
         <v>782</v>
       </c>
-      <c r="B204" t="s">
-        <v>732</v>
-      </c>
-      <c r="C204" t="s">
-        <v>733</v>
-      </c>
-      <c r="D204" t="s">
-        <v>783</v>
-      </c>
       <c r="E204" t="s">
+        <v>747</v>
+      </c>
+      <c r="F204" t="s">
+        <v>735</v>
+      </c>
+      <c r="G204" t="s">
         <v>748</v>
       </c>
-      <c r="F204" t="s">
-        <v>736</v>
-      </c>
-      <c r="G204" t="s">
-        <v>749</v>
-      </c>
       <c r="H204" s="3" t="s">
         <v>53</v>
       </c>
@@ -10616,31 +10619,31 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>783</v>
+      </c>
+      <c r="B205" t="s">
+        <v>731</v>
+      </c>
+      <c r="C205" t="s">
+        <v>732</v>
+      </c>
+      <c r="D205" t="s">
         <v>784</v>
       </c>
-      <c r="B205" t="s">
-        <v>732</v>
-      </c>
-      <c r="C205" t="s">
-        <v>733</v>
-      </c>
-      <c r="D205" t="s">
-        <v>785</v>
-      </c>
       <c r="E205" t="s">
+        <v>751</v>
+      </c>
+      <c r="F205" t="s">
+        <v>735</v>
+      </c>
+      <c r="G205" t="s">
         <v>752</v>
       </c>
-      <c r="F205" t="s">
-        <v>736</v>
-      </c>
-      <c r="G205" t="s">
-        <v>753</v>
-      </c>
       <c r="H205" s="3" t="s">
         <v>53</v>
       </c>
@@ -10648,31 +10651,31 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>785</v>
+      </c>
+      <c r="B206" t="s">
+        <v>731</v>
+      </c>
+      <c r="C206" t="s">
+        <v>732</v>
+      </c>
+      <c r="D206" t="s">
         <v>786</v>
       </c>
-      <c r="B206" t="s">
-        <v>732</v>
-      </c>
-      <c r="C206" t="s">
-        <v>733</v>
-      </c>
-      <c r="D206" t="s">
-        <v>787</v>
-      </c>
       <c r="E206" t="s">
+        <v>755</v>
+      </c>
+      <c r="F206" t="s">
+        <v>735</v>
+      </c>
+      <c r="G206" t="s">
         <v>756</v>
       </c>
-      <c r="F206" t="s">
-        <v>736</v>
-      </c>
-      <c r="G206" t="s">
-        <v>757</v>
-      </c>
       <c r="H206" s="3" t="s">
         <v>53</v>
       </c>
@@ -10680,31 +10683,31 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>787</v>
+      </c>
+      <c r="B207" t="s">
+        <v>731</v>
+      </c>
+      <c r="C207" t="s">
+        <v>732</v>
+      </c>
+      <c r="D207" t="s">
         <v>788</v>
       </c>
-      <c r="B207" t="s">
-        <v>732</v>
-      </c>
-      <c r="C207" t="s">
-        <v>733</v>
-      </c>
-      <c r="D207" t="s">
-        <v>789</v>
-      </c>
       <c r="E207" t="s">
+        <v>759</v>
+      </c>
+      <c r="F207" t="s">
+        <v>735</v>
+      </c>
+      <c r="G207" t="s">
         <v>760</v>
       </c>
-      <c r="F207" t="s">
-        <v>736</v>
-      </c>
-      <c r="G207" t="s">
-        <v>761</v>
-      </c>
       <c r="H207" s="3" t="s">
         <v>53</v>
       </c>
@@ -10712,31 +10715,31 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>789</v>
+      </c>
+      <c r="B208" t="s">
+        <v>731</v>
+      </c>
+      <c r="C208" t="s">
+        <v>732</v>
+      </c>
+      <c r="D208" t="s">
         <v>790</v>
       </c>
-      <c r="B208" t="s">
-        <v>732</v>
-      </c>
-      <c r="C208" t="s">
-        <v>733</v>
-      </c>
-      <c r="D208" t="s">
-        <v>791</v>
-      </c>
       <c r="E208" t="s">
+        <v>734</v>
+      </c>
+      <c r="F208" t="s">
         <v>735</v>
       </c>
-      <c r="F208" t="s">
+      <c r="G208" t="s">
         <v>736</v>
       </c>
-      <c r="G208" t="s">
-        <v>737</v>
-      </c>
       <c r="H208" s="3" t="s">
         <v>53</v>
       </c>
@@ -10744,39 +10747,39 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>722</v>
+        <v>578</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>791</v>
+      </c>
+      <c r="B209" t="s">
+        <v>731</v>
+      </c>
+      <c r="C209" t="s">
+        <v>732</v>
+      </c>
+      <c r="D209" t="s">
         <v>792</v>
       </c>
-      <c r="B209" t="s">
-        <v>732</v>
-      </c>
-      <c r="C209" t="s">
-        <v>733</v>
-      </c>
-      <c r="D209" t="s">
+      <c r="E209" t="s">
+        <v>739</v>
+      </c>
+      <c r="F209" t="s">
+        <v>735</v>
+      </c>
+      <c r="G209" t="s">
+        <v>740</v>
+      </c>
+      <c r="H209" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209" t="s">
         <v>793</v>
-      </c>
-      <c r="E209" t="s">
-        <v>740</v>
-      </c>
-      <c r="F209" t="s">
-        <v>736</v>
-      </c>
-      <c r="G209" t="s">
-        <v>741</v>
-      </c>
-      <c r="H209" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I209">
-        <v>1</v>
-      </c>
-      <c r="J209" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -10784,23 +10787,23 @@
         <v>794</v>
       </c>
       <c r="B210" t="s">
+        <v>731</v>
+      </c>
+      <c r="C210" t="s">
         <v>732</v>
-      </c>
-      <c r="C210" t="s">
-        <v>733</v>
       </c>
       <c r="D210" t="s">
         <v>795</v>
       </c>
       <c r="E210" t="s">
+        <v>743</v>
+      </c>
+      <c r="F210" t="s">
+        <v>735</v>
+      </c>
+      <c r="G210" t="s">
         <v>744</v>
       </c>
-      <c r="F210" t="s">
-        <v>736</v>
-      </c>
-      <c r="G210" t="s">
-        <v>745</v>
-      </c>
       <c r="H210" s="3" t="s">
         <v>53</v>
       </c>
@@ -10808,7 +10811,7 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -10816,23 +10819,23 @@
         <v>796</v>
       </c>
       <c r="B211" t="s">
+        <v>731</v>
+      </c>
+      <c r="C211" t="s">
         <v>732</v>
-      </c>
-      <c r="C211" t="s">
-        <v>733</v>
       </c>
       <c r="D211" t="s">
         <v>797</v>
       </c>
       <c r="E211" t="s">
+        <v>747</v>
+      </c>
+      <c r="F211" t="s">
+        <v>735</v>
+      </c>
+      <c r="G211" t="s">
         <v>748</v>
       </c>
-      <c r="F211" t="s">
-        <v>736</v>
-      </c>
-      <c r="G211" t="s">
-        <v>749</v>
-      </c>
       <c r="H211" s="3" t="s">
         <v>53</v>
       </c>
@@ -10840,7 +10843,7 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -10848,23 +10851,23 @@
         <v>798</v>
       </c>
       <c r="B212" t="s">
+        <v>731</v>
+      </c>
+      <c r="C212" t="s">
         <v>732</v>
-      </c>
-      <c r="C212" t="s">
-        <v>733</v>
       </c>
       <c r="D212" t="s">
         <v>799</v>
       </c>
       <c r="E212" t="s">
+        <v>751</v>
+      </c>
+      <c r="F212" t="s">
+        <v>735</v>
+      </c>
+      <c r="G212" t="s">
         <v>752</v>
       </c>
-      <c r="F212" t="s">
-        <v>736</v>
-      </c>
-      <c r="G212" t="s">
-        <v>753</v>
-      </c>
       <c r="H212" s="3" t="s">
         <v>53</v>
       </c>
@@ -10872,7 +10875,7 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -10880,23 +10883,23 @@
         <v>800</v>
       </c>
       <c r="B213" t="s">
+        <v>731</v>
+      </c>
+      <c r="C213" t="s">
         <v>732</v>
-      </c>
-      <c r="C213" t="s">
-        <v>733</v>
       </c>
       <c r="D213" t="s">
         <v>801</v>
       </c>
       <c r="E213" t="s">
+        <v>755</v>
+      </c>
+      <c r="F213" t="s">
+        <v>735</v>
+      </c>
+      <c r="G213" t="s">
         <v>756</v>
       </c>
-      <c r="F213" t="s">
-        <v>736</v>
-      </c>
-      <c r="G213" t="s">
-        <v>757</v>
-      </c>
       <c r="H213" s="3" t="s">
         <v>53</v>
       </c>
@@ -10904,7 +10907,7 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -10912,23 +10915,23 @@
         <v>802</v>
       </c>
       <c r="B214" t="s">
+        <v>731</v>
+      </c>
+      <c r="C214" t="s">
         <v>732</v>
-      </c>
-      <c r="C214" t="s">
-        <v>733</v>
       </c>
       <c r="D214" t="s">
         <v>803</v>
       </c>
       <c r="E214" t="s">
+        <v>759</v>
+      </c>
+      <c r="F214" t="s">
+        <v>735</v>
+      </c>
+      <c r="G214" t="s">
         <v>760</v>
       </c>
-      <c r="F214" t="s">
-        <v>736</v>
-      </c>
-      <c r="G214" t="s">
-        <v>761</v>
-      </c>
       <c r="H214" s="3" t="s">
         <v>53</v>
       </c>
@@ -10936,7 +10939,7 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -10944,23 +10947,23 @@
         <v>804</v>
       </c>
       <c r="B215" t="s">
+        <v>731</v>
+      </c>
+      <c r="C215" t="s">
         <v>732</v>
-      </c>
-      <c r="C215" t="s">
-        <v>733</v>
       </c>
       <c r="D215" t="s">
         <v>805</v>
       </c>
       <c r="E215" t="s">
+        <v>734</v>
+      </c>
+      <c r="F215" t="s">
         <v>735</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>736</v>
       </c>
-      <c r="G215" t="s">
-        <v>737</v>
-      </c>
       <c r="H215" s="3" t="s">
         <v>53</v>
       </c>
@@ -10968,7 +10971,7 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -10976,23 +10979,23 @@
         <v>806</v>
       </c>
       <c r="B216" t="s">
+        <v>731</v>
+      </c>
+      <c r="C216" t="s">
         <v>732</v>
-      </c>
-      <c r="C216" t="s">
-        <v>733</v>
       </c>
       <c r="D216" t="s">
         <v>807</v>
       </c>
       <c r="E216" t="s">
+        <v>739</v>
+      </c>
+      <c r="F216" t="s">
+        <v>735</v>
+      </c>
+      <c r="G216" t="s">
         <v>740</v>
       </c>
-      <c r="F216" t="s">
-        <v>736</v>
-      </c>
-      <c r="G216" t="s">
-        <v>741</v>
-      </c>
       <c r="H216" s="3" t="s">
         <v>53</v>
       </c>
@@ -11000,7 +11003,7 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -11008,23 +11011,23 @@
         <v>808</v>
       </c>
       <c r="B217" t="s">
+        <v>731</v>
+      </c>
+      <c r="C217" t="s">
         <v>732</v>
-      </c>
-      <c r="C217" t="s">
-        <v>733</v>
       </c>
       <c r="D217" t="s">
         <v>809</v>
       </c>
       <c r="E217" t="s">
+        <v>743</v>
+      </c>
+      <c r="F217" t="s">
+        <v>735</v>
+      </c>
+      <c r="G217" t="s">
         <v>744</v>
       </c>
-      <c r="F217" t="s">
-        <v>736</v>
-      </c>
-      <c r="G217" t="s">
-        <v>745</v>
-      </c>
       <c r="H217" s="3" t="s">
         <v>53</v>
       </c>
@@ -11032,7 +11035,7 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -11040,23 +11043,23 @@
         <v>810</v>
       </c>
       <c r="B218" t="s">
+        <v>731</v>
+      </c>
+      <c r="C218" t="s">
         <v>732</v>
-      </c>
-      <c r="C218" t="s">
-        <v>733</v>
       </c>
       <c r="D218" t="s">
         <v>811</v>
       </c>
       <c r="E218" t="s">
+        <v>747</v>
+      </c>
+      <c r="F218" t="s">
+        <v>735</v>
+      </c>
+      <c r="G218" t="s">
         <v>748</v>
       </c>
-      <c r="F218" t="s">
-        <v>736</v>
-      </c>
-      <c r="G218" t="s">
-        <v>749</v>
-      </c>
       <c r="H218" s="3" t="s">
         <v>53</v>
       </c>
@@ -11064,7 +11067,7 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -11072,23 +11075,23 @@
         <v>812</v>
       </c>
       <c r="B219" t="s">
+        <v>731</v>
+      </c>
+      <c r="C219" t="s">
         <v>732</v>
-      </c>
-      <c r="C219" t="s">
-        <v>733</v>
       </c>
       <c r="D219" t="s">
         <v>813</v>
       </c>
       <c r="E219" t="s">
+        <v>751</v>
+      </c>
+      <c r="F219" t="s">
+        <v>735</v>
+      </c>
+      <c r="G219" t="s">
         <v>752</v>
       </c>
-      <c r="F219" t="s">
-        <v>736</v>
-      </c>
-      <c r="G219" t="s">
-        <v>753</v>
-      </c>
       <c r="H219" s="3" t="s">
         <v>53</v>
       </c>
@@ -11096,7 +11099,7 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -11104,23 +11107,23 @@
         <v>814</v>
       </c>
       <c r="B220" t="s">
+        <v>731</v>
+      </c>
+      <c r="C220" t="s">
         <v>732</v>
-      </c>
-      <c r="C220" t="s">
-        <v>733</v>
       </c>
       <c r="D220" t="s">
         <v>815</v>
       </c>
       <c r="E220" t="s">
+        <v>755</v>
+      </c>
+      <c r="F220" t="s">
+        <v>735</v>
+      </c>
+      <c r="G220" t="s">
         <v>756</v>
       </c>
-      <c r="F220" t="s">
-        <v>736</v>
-      </c>
-      <c r="G220" t="s">
-        <v>757</v>
-      </c>
       <c r="H220" s="3" t="s">
         <v>53</v>
       </c>
@@ -11128,7 +11131,7 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -11136,23 +11139,23 @@
         <v>816</v>
       </c>
       <c r="B221" t="s">
+        <v>731</v>
+      </c>
+      <c r="C221" t="s">
         <v>732</v>
-      </c>
-      <c r="C221" t="s">
-        <v>733</v>
       </c>
       <c r="D221" t="s">
         <v>817</v>
       </c>
       <c r="E221" t="s">
+        <v>759</v>
+      </c>
+      <c r="F221" t="s">
+        <v>735</v>
+      </c>
+      <c r="G221" t="s">
         <v>760</v>
       </c>
-      <c r="F221" t="s">
-        <v>736</v>
-      </c>
-      <c r="G221" t="s">
-        <v>761</v>
-      </c>
       <c r="H221" s="3" t="s">
         <v>53</v>
       </c>
@@ -11160,7 +11163,7 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -11192,7 +11195,7 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -11224,7 +11227,7 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -11256,7 +11259,7 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -11288,7 +11291,7 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -11320,7 +11323,7 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -11352,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -11384,7 +11387,7 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -11416,7 +11419,7 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -11448,7 +11451,7 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -11480,7 +11483,7 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -11512,7 +11515,7 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -11544,7 +11547,7 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
@@ -11576,7 +11579,7 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -11608,7 +11611,7 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
@@ -11640,7 +11643,7 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
@@ -11672,7 +11675,7 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
@@ -11704,7 +11707,7 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -11736,7 +11739,7 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
@@ -11768,7 +11771,7 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -11800,7 +11803,7 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -11832,7 +11835,7 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -11864,7 +11867,7 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
@@ -11896,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
@@ -11928,7 +11931,7 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
@@ -11960,7 +11963,7 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
@@ -11992,7 +11995,7 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
@@ -12024,7 +12027,7 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
@@ -12056,7 +12059,7 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
@@ -12088,7 +12091,7 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
@@ -12120,7 +12123,7 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>722</v>
+        <v>793</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
@@ -12149,7 +12152,7 @@
         <v>53</v>
       </c>
       <c r="I252">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="J252" t="s">
         <v>948</v>
@@ -13304,12 +13307,12 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>1102</v>
+        <v>948</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B289" t="s">
         <v>1066</v>
@@ -13318,17 +13321,17 @@
         <v>1067</v>
       </c>
       <c r="D289" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E289" t="s">
         <v>1104</v>
       </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>1105</v>
       </c>
-      <c r="F289" t="s">
+      <c r="G289" t="s">
         <v>1106</v>
       </c>
-      <c r="G289" t="s">
-        <v>1107</v>
-      </c>
       <c r="H289" s="3" t="s">
         <v>53</v>
       </c>
@@ -13336,12 +13339,12 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>1102</v>
+        <v>948</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B290" t="s">
         <v>1066</v>
@@ -13350,17 +13353,17 @@
         <v>1067</v>
       </c>
       <c r="D290" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E290" t="s">
         <v>1109</v>
       </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
         <v>1110</v>
       </c>
-      <c r="F290" t="s">
+      <c r="G290" t="s">
         <v>1111</v>
       </c>
-      <c r="G290" t="s">
-        <v>1112</v>
-      </c>
       <c r="H290" s="3" t="s">
         <v>53</v>
       </c>
@@ -13368,12 +13371,12 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>1102</v>
+        <v>948</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B291" t="s">
         <v>1066</v>
@@ -13382,17 +13385,17 @@
         <v>1067</v>
       </c>
       <c r="D291" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E291" t="s">
         <v>1114</v>
       </c>
-      <c r="E291" t="s">
+      <c r="F291" t="s">
         <v>1115</v>
       </c>
-      <c r="F291" t="s">
+      <c r="G291" t="s">
         <v>1116</v>
       </c>
-      <c r="G291" t="s">
-        <v>1117</v>
-      </c>
       <c r="H291" s="3" t="s">
         <v>53</v>
       </c>
@@ -13400,12 +13403,12 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>1102</v>
+        <v>948</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B292" t="s">
         <v>1066</v>
@@ -13414,7 +13417,7 @@
         <v>1067</v>
       </c>
       <c r="D292" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E292" t="s">
         <v>1069</v>
@@ -13423,7 +13426,7 @@
         <v>1070</v>
       </c>
       <c r="G292" t="s">
-        <v>1120</v>
+        <v>1071</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>53</v>
@@ -13432,12 +13435,12 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>1102</v>
+        <v>948</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B293" t="s">
         <v>1066</v>
@@ -13446,7 +13449,7 @@
         <v>1067</v>
       </c>
       <c r="D293" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="E293" t="s">
         <v>1074</v>
@@ -13455,7 +13458,7 @@
         <v>1075</v>
       </c>
       <c r="G293" t="s">
-        <v>1123</v>
+        <v>1076</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>53</v>
@@ -13464,12 +13467,12 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>1102</v>
+        <v>948</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="B294" t="s">
         <v>1066</v>
@@ -13478,7 +13481,7 @@
         <v>1067</v>
       </c>
       <c r="D294" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="E294" t="s">
         <v>1079</v>
@@ -13487,7 +13490,7 @@
         <v>1080</v>
       </c>
       <c r="G294" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="H294" s="3" t="s">
         <v>53</v>
@@ -13496,12 +13499,12 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>1102</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B295" t="s">
         <v>1066</v>
@@ -13510,7 +13513,7 @@
         <v>1067</v>
       </c>
       <c r="D295" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="E295" t="s">
         <v>1084</v>
@@ -13519,7 +13522,7 @@
         <v>1085</v>
       </c>
       <c r="G295" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>53</v>
@@ -13528,12 +13531,12 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>1102</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B296" t="s">
         <v>1066</v>
@@ -13542,7 +13545,7 @@
         <v>1067</v>
       </c>
       <c r="D296" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="E296" t="s">
         <v>1089</v>
@@ -13551,7 +13554,7 @@
         <v>1090</v>
       </c>
       <c r="G296" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>53</v>
@@ -13560,12 +13563,12 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>1102</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B297" t="s">
         <v>1066</v>
@@ -13574,7 +13577,7 @@
         <v>1067</v>
       </c>
       <c r="D297" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="E297" t="s">
         <v>1094</v>
@@ -13583,7 +13586,7 @@
         <v>1095</v>
       </c>
       <c r="G297" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>53</v>
@@ -13592,12 +13595,12 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>1102</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B298" t="s">
         <v>1066</v>
@@ -13606,7 +13609,7 @@
         <v>1067</v>
       </c>
       <c r="D298" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="E298" t="s">
         <v>1099</v>
@@ -13615,7 +13618,7 @@
         <v>1100</v>
       </c>
       <c r="G298" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>53</v>
@@ -13624,12 +13627,12 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>1102</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B299" t="s">
         <v>1066</v>
@@ -13638,16 +13641,16 @@
         <v>1067</v>
       </c>
       <c r="D299" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="E299" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F299" t="s">
         <v>1105</v>
       </c>
-      <c r="F299" t="s">
-        <v>1106</v>
-      </c>
       <c r="G299" t="s">
-        <v>1107</v>
+        <v>1139</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>53</v>
@@ -13656,12 +13659,12 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>1102</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B300" t="s">
         <v>1066</v>
@@ -13670,17 +13673,17 @@
         <v>1067</v>
       </c>
       <c r="D300" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E300" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F300" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G300" t="s">
         <v>1142</v>
       </c>
-      <c r="E300" t="s">
-        <v>1110</v>
-      </c>
-      <c r="F300" t="s">
-        <v>1111</v>
-      </c>
-      <c r="G300" t="s">
-        <v>1112</v>
-      </c>
       <c r="H300" s="3" t="s">
         <v>53</v>
       </c>
@@ -13688,7 +13691,7 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>1102</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -13705,13 +13708,13 @@
         <v>1144</v>
       </c>
       <c r="E301" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F301" t="s">
         <v>1115</v>
       </c>
-      <c r="F301" t="s">
-        <v>1116</v>
-      </c>
       <c r="G301" t="s">
-        <v>1117</v>
+        <v>1145</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>53</v>
@@ -13720,7 +13723,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>1102</v>
+        <v>1124</v>
       </c>
     </row>
   </sheetData>
